--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -18,6 +18,7 @@
     <sheet name="京都-水戸_822" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="町田-浦和_823" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="G大阪-広島_829" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="鹿島-G大阪_1009" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8532,6 +8533,154 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>エグゼクティブ・指定</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>カテゴリー１・指定</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>カテゴリー２・指定</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>カテゴリー３・指定</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>カテゴリー４・指定</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>カテゴリー５・指定</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>カテゴリー６・指定</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ホームサポーターズシート・指定</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ホームサポシコーナー・指定</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ホームゴール裏北・指定</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ビジター専用シート・指定</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>車椅子席</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-30 06:01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -19,6 +19,19 @@
     <sheet name="町田-浦和_823" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="G大阪-広島_829" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="鹿島-G大阪_1009" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="C大阪-横浜FM_1010" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="京都-町田_1010" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="福岡-岡山_1010" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="川崎F-名古屋_1011" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="東京V-広島_1011" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="C大阪-川崎F_1017" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="東京V-FC東京_1017" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="町田-福岡_1018" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="川崎F-神戸_1021" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="福岡-G大阪_1021" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="京都-鹿島_1021" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="C大阪-千葉_1025" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="C大阪-FC東京_1121" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8539,7 +8552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:AE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8555,55 +8568,145 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>エグゼクティブ・指定 北</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>カテゴリー１・指定</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>カテゴリー１・指定 中央</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>カテゴリー２・指定</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>カテゴリー２・指定 中央</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>カテゴリー３・指定</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>カテゴリー３・指定 北側</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>カテゴリー３・指定 南側（ホーム側）</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>カテゴリー４・指定</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>カテゴリー４・指定 北側</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>カテゴリー４・指定 南側（ホーム側）</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>カテゴリー５・指定</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>カテゴリー５・指定 北側</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>カテゴリー５・指定 南側（ホーム側）</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>カテゴリー６・指定</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>カテゴリー６・指定 北側</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>カテゴリー６・指定 南側（ホーム側）</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>ホームサポーターズシート・指定</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ホームサポーターズシート・指定 上層　南</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ホームサポーターズシート・指定 下層　南</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ホームサポシコーナー・指定 下層メイン南</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>ホームサポシコーナー・指定</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ホームサポシコーナー・指定 下層バック南</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ホームサポシコーナー・指定 下層メイン北</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ホームゴール裏北・指定 下層　北</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
         <is>
           <t>ホームゴール裏北・指定</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ビジター専用シート・指定 下層　北</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ビジター専用シート・指定</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>車椅子席</t>
         </is>
@@ -8620,59 +8723,2016 @@
           <t>9,600 完売</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート(ホーム)前方</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート（ホーム）</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席前方</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席前方</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席前方</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席前方</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ホームメインセンターA指定席</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ホームメイン北A指定席</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ホームメイン南A指定席</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>バックセンターシート下段ホーム</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>バックセンターシート上段ホーム</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席下段</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席上段</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席下段</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席上段</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席下段</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席上段</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席下段</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席上段</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ホームサポーター指定席</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ホームサポーター自由席</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ホーム南スタンド自由席</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ビジターサポーター指定席</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートAホーム</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートBホーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9,200 完売</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2,300</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>サンガプレミアムシート</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>サンガシート</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>メインＳ指定席北側</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>メインＳ指定席南側</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>バックエキサイティングシート</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>バックＳ指定席</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>バックＡ指定席北側</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>バックＡ指定席南側</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>バック上層フロントシート</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>バック上層Ｓ指定席</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>バック上層Ａ指定席北側</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>バック上層Ａ指定席南側</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>バルコニー指定席１・４</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>バルコニー指定席２・３</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>バルコニー上層指定席</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホーム指定席（立見可能）</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ホーム上層指定席</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>南サイド指定席</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>南サイドホーム上層自由席</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ビジター指定席</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>プレミアムシート指定</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>アビスパシート指定</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>メインスタンド指定（Ｍ５） ベンチ左側</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>メインスタンド指定（Ｍ２） ベンチ右側</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>メインスタンド指定（Ｍ６） ベンチ左側</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>メインスタンド自由（Ｍ６）</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>メインスタンド指定（Ｍ１） ベンチ右側</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>メインスタンド自由（Ｍ１）</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート指定</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ピッチサイドシート指定（Ｂ２）</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ピッチサイドシート指定（Ｂ６）</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>柴田産業Axion指定</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>バックスタンド自由（Ｂ１）</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>バックスタンド自由（Ｂ７）</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ホームゴール裏自由</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ウェルカムシート自由</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>アウェイゴール裏自由</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>車いす席　平面駐車場付</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>車いす席　立体駐車場付</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ＳＳＳ指定</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>メインＳＳ指定下層北側 メイン下層北側</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>メインＳＳ指定下層南側 メイン下層南側</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>メインＳＳ指定上層中央 メイン上層中央</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>バックＳＳ指定 バック２階中央</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>メインＳ指定北側 メイン下層北側</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>メインＳ指定北側 メイン上層北側</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>メインＳ指定南側 メイン上層南側</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>メインＳ指定南側 メイン下層南側</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>バックＳ指定北側 バック２階北</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>バックＳ指定南側 バック２階南</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ＳＧ指定 バック２階北</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ＳＡ指定北側 ゴール裏２階北</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ＳＡ指定南側 ゴール裏２階南</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ホームＡ指定 バック１階中央</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ホームＡ指定 バック１階南</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホームＡ自由 サイド・バック1階</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>セブンイレブンピッチサイド席</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ビジターＳ指定 メイン下層南側</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ビジターＳＡ指定 ゴール裏２階南</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ビジターＡ自由 ゴール裏1階南 立見</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>PREファミリーシート３</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>PREファミリーシート４</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>PREファミリーシート６</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>グループシート４</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ごちクルグループシート６</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ペアシート北側 北側</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>X NETWORKペアシート 南側 南側</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>テーブル付ペアシート メイン上層南側</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>テーブル付ペアシート メイン下層南側</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>ＴＨＥＲＭＯＳ パーティーシート 南側</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>メイン車椅子席</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>バック車椅子席</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>メインペア指定ホーム</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>メインSS指定ホーム1階</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>メインSS指定ホーム2階</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>メインSS指定ミックス1階</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>メインSS指定ミックス2階</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>メインS指定ホーム1階</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>メインホーム自由（2階）</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>メインS指定ミックス1階</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>メインS指定ミックス2階</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>バックホーム指定センター</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>バックホーム自由</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ゴール裏ホーム自由</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>サイドホーム自由</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ゴール裏ビジター指定</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ピッチサイドシートホーム</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ピッチサイドシートビジター</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>7,000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>9,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>6,000</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>10,300</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>11,000 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート(ホーム)前方</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート（ホーム）</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席前方</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席前方</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席前方</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席前方</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ホームメインセンターA指定席</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ホームメイン北A指定席</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ホームメイン南A指定席</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>バックセンターシート下段ホーム</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>バックセンターシート上段ホーム</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席下段</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席上段</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席下段</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席上段</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席下段</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席上段</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席下段</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席上段</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ホームサポーター指定席</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ホームサポーター自由席</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ホーム南スタンド自由席</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ビジターサポーター指定席</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートAホーム</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートBホーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6,400</t>
+          <t>8,500</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,400</t>
+          <t>9,800</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>5,100</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>メインペア指定ホーム</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>メインSS指定ホーム1階</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>メインSS指定ホーム2階</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>メインSS指定ミックス1階</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>メインSS指定ミックス2階</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>メインS指定ホーム1階</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>メインホーム自由（2階）</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>メインS指定ミックス1階</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>メインS指定ミックス2階</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>バックホーム指定センター</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>バックホーム自由</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ゴール裏ホーム自由</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>サイドホーム自由</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ピッチサイドシートホーム特典付</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ピッチサイドシートビジター</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ゴール裏ビジター指定</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>10,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>4,700</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>8,800 [変動]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>8,100 [変動]</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>4,400</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
         </is>
       </c>
     </row>
@@ -10531,6 +12591,1614 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ピッチサイドシート</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>プレミアムシート</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>カテゴリー１　東</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>カテゴリー１　西</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>カテゴリー２　東</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>カテゴリー２　西</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>カテゴリー３</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>カテゴリー４</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>カテゴリー５</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ゼルビアサポーターズシート立見席</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ビジターサポーターズシート</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>メイン車イス席</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>バック車イス席</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AH2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ＳＳＳ指定</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>メインＳＳ指定下層北側 メイン下層北側</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>メインＳＳ指定下層南側 メイン下層南側</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>メインＳＳ指定上層中央 メイン上層中央</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>バックＳＳ指定 バック２階中央</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>メインＳ指定北側 メイン下層北側</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>メインＳ指定北側 メイン上層北側</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>メインＳ指定南側 メイン上層南側</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>メインＳ指定南側 メイン下層南側</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>バックＳ指定北側 バック２階北</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>バックＳ指定南側 バック２階南</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ＳＧ指定 バック２階北</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ＳＡ指定北側 ゴール裏２階北</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ＳＡ指定南側 ゴール裏２階南</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ホームＡ指定 バック１階中央</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ホームＡ指定 バック１階南</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホームＡ自由 サイド・バック1階</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>セブンイレブンピッチサイド席</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ビジターＳ指定 メイン下層南側</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ビジターＳＡ指定 ゴール裏２階南</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ビジターＡ自由 ゴール裏1階南 立見</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>PREファミリーシート３</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>PREファミリーシート４</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>PREファミリーシート６</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>グループシート４</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ごちクルグループシート６</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ペアシート北側 北側</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>X NETWORKペアシート 南側 南側</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>テーブル付ペアシート メイン上層南側</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>テーブル付ペアシート メイン下層南側</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>ＴＨＥＲＭＯＳ パーティーシート 南側</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>メイン車椅子席</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>バック車椅子席</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>プレミアムシート指定</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>アビスパシート指定</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>メインスタンド指定（Ｍ５） ベンチ左側</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>メインスタンド指定（Ｍ２） ベンチ右側</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>メインスタンド指定（Ｍ６） ベンチ左側</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>メインスタンド自由（Ｍ６）</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>メインスタンド指定（Ｍ１） ベンチ右側</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>メインスタンド自由（Ｍ１）</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート指定</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ピッチサイドシート指定（Ｂ２）</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ピッチサイドシート指定（Ｂ６）</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>柴田産業Axion指定</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>バックスタンド自由（Ｂ１）</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>バックスタンド自由（Ｂ７）</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ホームゴール裏自由</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ウェルカムシート自由</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>アウェイゴール裏自由</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>車いす席　平面駐車場付</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>車いす席　立体駐車場付</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>サンガプレミアムシート</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>サンガシート</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>メインＳ指定席北側</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>メインＳ指定席南側</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>バックエキサイティングシート</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>バックＳ指定席</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>バックＡ指定席北側</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>バックＡ指定席南側</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>バック上層フロントシート</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>バック上層Ｓ指定席</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>バック上層Ａ指定席北側</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>バック上層Ａ指定席南側</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>バルコニー指定席１・４</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>バルコニー指定席２・３</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>バルコニー上層指定席</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホーム指定席（立見可能）</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ホーム上層指定席</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>南サイド指定席</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>南サイドホーム上層自由席</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ビジター指定席</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート(ホーム)前方</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート（ホーム）</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席前方</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席前方</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席前方</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席前方</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ホームメインセンターA指定席</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ホームメイン北A指定席</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ホームメイン南A指定席</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>バックセンターシート下段ホーム</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>バックセンターシート上段ホーム</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席下段</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席上段</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席下段</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席上段</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席下段</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席上段</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席下段</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席上段</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ホームサポーター指定席</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ホームサポーター自由席</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ホーム南スタンド自由席</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ビジターサポーター指定席</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートAホーム</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートBホーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート(ホーム)前方</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート（ホーム）</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席前方</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席前方</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席前方</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席前方</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ホームメインセンターA指定席</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ホームメイン北A指定席</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ホームメイン南A指定席</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>バックセンターシート下段ホーム</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>バックセンターシート上段ホーム</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席下段</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席上段</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席下段</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席上段</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席下段</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席上段</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席下段</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席上段</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ホームサポーター指定席</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ホームサポーター自由席</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ホーム南スタンド自由席</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ビジターサポーター指定席</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートAホーム</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートBホーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:33</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -8552,7 +8552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8905,6 +8905,119 @@
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -8921,7 +9034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9223,6 +9336,158 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9,200 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2,300</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -9239,7 +9504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9461,6 +9726,118 @@
         </is>
       </c>
       <c r="V2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -9477,7 +9854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9679,6 +10056,108 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -9695,7 +10174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10037,6 +10516,178 @@
         </is>
       </c>
       <c r="AH2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -10053,7 +10704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10225,6 +10876,93 @@
         </is>
       </c>
       <c r="Q2" t="inlineStr">
+        <is>
+          <t>11,000 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>10,300</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>11,000 [変動] 完売</t>
         </is>
@@ -10241,7 +10979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10543,6 +11281,158 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9,800</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -10559,7 +11449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10731,6 +11621,93 @@
         </is>
       </c>
       <c r="Q2" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>5,500 [変動]</t>
         </is>
@@ -12597,7 +13574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12739,6 +13716,78 @@
         </is>
       </c>
       <c r="N2" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
@@ -12755,7 +13804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13097,6 +14146,178 @@
         </is>
       </c>
       <c r="AH2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -13113,7 +14334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13315,6 +14536,108 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -13331,7 +14654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13553,6 +14876,118 @@
         </is>
       </c>
       <c r="V2" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>4,200 完売</t>
         </is>
@@ -13569,7 +15004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13871,6 +15306,158 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -13887,7 +15474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14189,6 +15776,158 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -8552,7 +8552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE4"/>
+  <dimension ref="A1:AE5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9018,6 +9018,119 @@
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:46</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -9034,7 +9147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9488,6 +9601,158 @@
         </is>
       </c>
       <c r="AD3" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:46</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9,200 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2,300</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -9504,7 +9769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9838,6 +10103,118 @@
         </is>
       </c>
       <c r="V3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:47</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -9854,7 +10231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10158,6 +10535,108 @@
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:46</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -10174,7 +10653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10688,6 +11167,178 @@
         </is>
       </c>
       <c r="AH3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:47</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -10704,7 +11355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10963,6 +11614,93 @@
         </is>
       </c>
       <c r="Q3" t="inlineStr">
+        <is>
+          <t>11,000 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:47</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>9,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>10,300</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>11,000 [変動] 完売</t>
         </is>
@@ -10979,7 +11717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11433,6 +12171,158 @@
         </is>
       </c>
       <c r="AD3" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:46</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9,800</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -11449,7 +12339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11708,6 +12598,93 @@
         </is>
       </c>
       <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:47</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>10,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>5,500 [変動]</t>
         </is>
@@ -13574,7 +14551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13788,6 +14765,78 @@
         </is>
       </c>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:47</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
@@ -13804,7 +14853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14318,6 +15367,178 @@
         </is>
       </c>
       <c r="AH3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:47</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -14334,7 +15555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14638,6 +15859,108 @@
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:46</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -14654,7 +15977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14988,6 +16311,118 @@
         </is>
       </c>
       <c r="V3" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:47</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>4,200 完売</t>
         </is>
@@ -15004,7 +16439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15458,6 +16893,158 @@
         </is>
       </c>
       <c r="AD3" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:46</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -15474,7 +17061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15928,6 +17515,158 @@
         </is>
       </c>
       <c r="AD3" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:46</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -8552,7 +8552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE5"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9131,6 +9131,119 @@
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:00</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -9147,7 +9260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9753,6 +9866,158 @@
         </is>
       </c>
       <c r="AD4" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9,200 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -9769,7 +10034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10215,6 +10480,118 @@
         </is>
       </c>
       <c r="V4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -10231,7 +10608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10637,6 +11014,108 @@
         </is>
       </c>
       <c r="T4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -10653,7 +11132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:AH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11339,6 +11818,178 @@
         </is>
       </c>
       <c r="AH4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -11355,7 +12006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11701,6 +12352,93 @@
         </is>
       </c>
       <c r="Q4" t="inlineStr">
+        <is>
+          <t>11,000 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>10,300</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>11,000 [変動] 完売</t>
         </is>
@@ -11717,7 +12455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12325,6 +13063,158 @@
       <c r="AD4" t="inlineStr">
         <is>
           <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>9,800</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
         </is>
       </c>
     </row>
@@ -12339,7 +13229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12685,6 +13575,93 @@
         </is>
       </c>
       <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>5,500 [変動]</t>
         </is>
@@ -14551,7 +15528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14837,6 +15814,78 @@
         </is>
       </c>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
@@ -14853,7 +15902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:AH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15539,6 +16588,178 @@
         </is>
       </c>
       <c r="AH4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -15555,7 +16776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15961,6 +17182,108 @@
         </is>
       </c>
       <c r="T4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -15977,7 +17300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16423,6 +17746,118 @@
         </is>
       </c>
       <c r="V4" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>4,200 完売</t>
         </is>
@@ -16439,7 +17874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17045,6 +18480,158 @@
         </is>
       </c>
       <c r="AD4" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -17061,7 +18648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17667,6 +19254,158 @@
         </is>
       </c>
       <c r="AD4" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -8552,7 +8552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AE7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9244,6 +9244,119 @@
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:41</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -9260,7 +9373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10018,6 +10131,158 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:41</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,200 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -10034,7 +10299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10592,6 +10857,118 @@
         </is>
       </c>
       <c r="V5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:41</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -10608,7 +10985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11116,6 +11493,108 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:41</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>13,800</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -11132,7 +11611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11990,6 +12469,178 @@
         </is>
       </c>
       <c r="AH5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:42</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>4,100 完売</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -12006,7 +12657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12439,6 +13090,93 @@
         </is>
       </c>
       <c r="Q5" t="inlineStr">
+        <is>
+          <t>11,000 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:41</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>9,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>10,300</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>11,000 [変動] 完売</t>
         </is>
@@ -12455,7 +13193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13213,6 +13951,158 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:41</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9,800</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -13229,7 +14119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13662,6 +14552,93 @@
         </is>
       </c>
       <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:42</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>5,500 [変動]</t>
         </is>
@@ -15528,7 +16505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15886,6 +16863,78 @@
         </is>
       </c>
       <c r="N5" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:42</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
@@ -15902,7 +16951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16760,6 +17809,178 @@
         </is>
       </c>
       <c r="AH5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:42</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -16776,7 +17997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17284,6 +18505,108 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:41</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -17300,7 +18623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17858,6 +19181,118 @@
         </is>
       </c>
       <c r="V5" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:41</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>4,200 完売</t>
         </is>
@@ -17874,7 +19309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18632,6 +20067,158 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:41</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -18648,7 +20235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19406,6 +20993,158 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 08:41</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -1,37 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="横浜FM-鹿島_807" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="福岡-神戸_808" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="名古屋-清水_808" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="C大阪-岡山_808" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="東京V-柏_814" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="川崎F-京都_815" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="岡山-長崎_815" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="FC東京-千葉_821" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="京都-水戸_822" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="町田-浦和_823" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="G大阪-広島_829" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="鹿島-G大阪_1009" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="C大阪-横浜FM_1010" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="京都-町田_1010" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="福岡-岡山_1010" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="川崎F-名古屋_1011" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="東京V-広島_1011" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="C大阪-川崎F_1017" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="東京V-FC東京_1017" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="町田-福岡_1018" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="川崎F-神戸_1021" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="福岡-G大阪_1021" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="京都-鹿島_1021" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="C大阪-千葉_1025" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="C大阪-FC東京_1121" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="横浜FM-鹿島_807" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福岡-神戸_808" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名古屋-清水_808" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C大阪-岡山_808" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="東京V-柏_814" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="川崎F-京都_815" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="岡山-長崎_815" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FC東京-千葉_821" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="京都-水戸_822" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="町田-浦和_823" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="G大阪-広島_829" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="鹿島-G大阪_1009" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C大阪-横浜FM_1010" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="京都-町田_1010" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福岡-岡山_1010" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="川崎F-名古屋_1011" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="東京V-広島_1011" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C大阪-川崎F_1017" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="東京V-FC東京_1017" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="町田-福岡_1018" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="川崎F-神戸_1021" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="福岡-G大阪_1021" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="京都-鹿島_1021" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C大阪-千葉_1025" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C大阪-FC東京_1121" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8552,7 +8552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE7"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9357,6 +9357,119 @@
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -9373,7 +9486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10283,6 +10396,158 @@
         </is>
       </c>
       <c r="AD6" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9,200 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -10299,7 +10564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10969,6 +11234,118 @@
         </is>
       </c>
       <c r="V6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -10985,7 +11362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11595,6 +11972,108 @@
         </is>
       </c>
       <c r="T6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>13,800</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -11611,7 +12090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH6"/>
+  <dimension ref="A1:AH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12641,6 +13120,178 @@
         </is>
       </c>
       <c r="AH6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4,100 完売</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -12657,7 +13308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13177,6 +13828,93 @@
         </is>
       </c>
       <c r="Q6" t="inlineStr">
+        <is>
+          <t>11,000 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>9,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>10,300</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>11,000 [変動] 完売</t>
         </is>
@@ -13193,7 +13931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14103,6 +14841,158 @@
         </is>
       </c>
       <c r="AD6" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -14119,7 +15009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14639,6 +15529,93 @@
         </is>
       </c>
       <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>5,500 [変動]</t>
         </is>
@@ -16505,7 +17482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16935,6 +17912,78 @@
         </is>
       </c>
       <c r="N6" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
@@ -16951,7 +18000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH6"/>
+  <dimension ref="A1:AH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17981,6 +19030,178 @@
         </is>
       </c>
       <c r="AH6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -17997,7 +19218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18607,6 +19828,108 @@
         </is>
       </c>
       <c r="T6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -18623,7 +19946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19295,6 +20618,118 @@
       <c r="V6" t="inlineStr">
         <is>
           <t>4,200 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4,200</t>
         </is>
       </c>
     </row>
@@ -19309,7 +20744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20219,6 +21654,158 @@
         </is>
       </c>
       <c r="AD6" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -20235,7 +21822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21145,6 +22732,158 @@
         </is>
       </c>
       <c r="AD6" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-04 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -8558,7 +8558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9589,6 +9589,119 @@
       </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:38</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -9605,7 +9718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10819,6 +10932,158 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,200 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -10835,7 +11100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11729,6 +11994,118 @@
         </is>
       </c>
       <c r="V8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -11745,7 +12122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12559,6 +12936,108 @@
         </is>
       </c>
       <c r="T8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13,800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -12575,7 +13054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH8"/>
+  <dimension ref="A1:AH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13949,6 +14428,178 @@
         </is>
       </c>
       <c r="AH8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>4,100 完売</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -13965,7 +14616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14659,6 +15310,93 @@
         </is>
       </c>
       <c r="Q8" t="inlineStr">
+        <is>
+          <t>11,000 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10,300</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>11,000 [変動] 完売</t>
         </is>
@@ -14675,7 +15413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15889,6 +16627,158 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -15905,7 +16795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16599,6 +17489,93 @@
         </is>
       </c>
       <c r="Q8" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>5,500 [変動]</t>
         </is>
@@ -18465,7 +19442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19039,6 +20016,78 @@
         </is>
       </c>
       <c r="N8" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
@@ -19055,7 +20104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19217,6 +20266,88 @@
         </is>
       </c>
       <c r="P2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -19233,7 +20364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH8"/>
+  <dimension ref="A1:AH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20607,6 +21738,178 @@
         </is>
       </c>
       <c r="AH8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -20623,7 +21926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21437,6 +22740,108 @@
         </is>
       </c>
       <c r="T8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -21453,7 +22858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22349,6 +23754,118 @@
       <c r="V8" t="inlineStr">
         <is>
           <t>4,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>4,400</t>
         </is>
       </c>
     </row>
@@ -22363,7 +23880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22545,6 +24062,98 @@
         </is>
       </c>
       <c r="R2" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>3,400</t>
         </is>
@@ -22561,7 +24170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23775,6 +25384,158 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -23791,7 +25552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23933,6 +25694,78 @@
         </is>
       </c>
       <c r="N2" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>3,080</t>
         </is>
@@ -23949,7 +25782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24131,6 +25964,98 @@
         </is>
       </c>
       <c r="R2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>3,200</t>
         </is>
@@ -24147,7 +26072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25361,6 +27286,158 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -26867,7 +28944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27049,6 +29126,98 @@
         </is>
       </c>
       <c r="R2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>3,200</t>
         </is>
@@ -27065,7 +29234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27367,6 +29536,158 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-05 20:39</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13,100 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -8558,7 +8558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9702,6 +9702,119 @@
       </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -9718,7 +9831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11084,6 +11197,158 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,200 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -11100,7 +11365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12106,6 +12371,118 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -12122,7 +12499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13038,6 +13415,108 @@
         </is>
       </c>
       <c r="T9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13,800</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -13054,7 +13533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH9"/>
+  <dimension ref="A1:AH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14600,6 +15079,178 @@
         </is>
       </c>
       <c r="AH9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>4,100 完売</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -14616,7 +15267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15397,6 +16048,93 @@
         </is>
       </c>
       <c r="Q9" t="inlineStr">
+        <is>
+          <t>11,000 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>10,300</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>11,000 [変動] 完売</t>
         </is>
@@ -15413,7 +16151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16779,6 +17517,158 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -16795,7 +17685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17576,6 +18466,93 @@
         </is>
       </c>
       <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>5,500 [変動]</t>
         </is>
@@ -19442,7 +20419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20088,6 +21065,78 @@
         </is>
       </c>
       <c r="N9" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
@@ -20104,7 +21153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20348,6 +21397,88 @@
         </is>
       </c>
       <c r="P3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -20364,7 +21495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH9"/>
+  <dimension ref="A1:AH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21910,6 +23041,178 @@
         </is>
       </c>
       <c r="AH9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -21926,7 +23229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22842,6 +24145,108 @@
         </is>
       </c>
       <c r="T9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -22858,7 +24263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23864,6 +25269,118 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>4,400</t>
         </is>
@@ -23880,7 +25397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24154,6 +25671,98 @@
         </is>
       </c>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>3,400</t>
         </is>
@@ -24170,7 +25779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25536,6 +27145,158 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -25552,7 +27313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25766,6 +27527,78 @@
         </is>
       </c>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>3,080</t>
         </is>
@@ -25782,7 +27615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26056,6 +27889,98 @@
         </is>
       </c>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>3,200</t>
         </is>
@@ -26072,7 +27997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27438,6 +29363,158 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -28944,7 +31021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29218,6 +31295,98 @@
         </is>
       </c>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>3,200</t>
         </is>
@@ -29234,7 +31403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29688,6 +31857,158 @@
         </is>
       </c>
       <c r="AD3" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13,100 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -6974,7 +6974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AE7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7666,6 +7666,119 @@
       </c>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -7682,7 +7795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8440,6 +8553,158 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,200 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2,400 完売</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -8456,7 +8721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9014,6 +9279,118 @@
         </is>
       </c>
       <c r="V5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -9030,7 +9407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9538,6 +9915,108 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>13,800</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>9,900 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -9554,7 +10033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10412,6 +10891,178 @@
         </is>
       </c>
       <c r="AH5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>4,100 完売</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -10428,7 +11079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10861,6 +11512,93 @@
         </is>
       </c>
       <c r="Q5" t="inlineStr">
+        <is>
+          <t>11,000 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>9,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>10,300</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>11,000 [変動] 完売</t>
         </is>
@@ -10877,7 +11615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11635,6 +12373,158 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -11651,7 +12541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12084,6 +12974,93 @@
         </is>
       </c>
       <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>5,500 [変動]</t>
         </is>
@@ -13440,7 +14417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13798,6 +14775,78 @@
         </is>
       </c>
       <c r="N5" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
@@ -13814,7 +14863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13976,6 +15025,88 @@
         </is>
       </c>
       <c r="P2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -13992,7 +15123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14850,6 +15981,178 @@
         </is>
       </c>
       <c r="AH5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -14866,7 +16169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15374,6 +16677,108 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -15390,7 +16795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15948,6 +17353,118 @@
         </is>
       </c>
       <c r="V5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>4,400</t>
         </is>
@@ -15964,7 +17481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16146,6 +17663,98 @@
         </is>
       </c>
       <c r="R2" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>3,400</t>
         </is>
@@ -16162,7 +17771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16920,6 +18529,158 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -16936,7 +18697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17078,6 +18839,78 @@
         </is>
       </c>
       <c r="N2" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>3,080</t>
         </is>
@@ -17094,7 +18927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17276,6 +19109,98 @@
         </is>
       </c>
       <c r="R2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>3,200</t>
         </is>
@@ -17292,7 +19217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18050,6 +19975,158 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -19146,7 +21223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19328,6 +21405,98 @@
         </is>
       </c>
       <c r="R2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>3,200</t>
         </is>
@@ -19344,7 +21513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19646,6 +21815,158 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13,100 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -6974,7 +6974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE7"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7779,6 +7779,119 @@
       </c>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -7795,7 +7908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8705,6 +8818,158 @@
         </is>
       </c>
       <c r="AD6" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9,200 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -8721,7 +8986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9391,6 +9656,118 @@
         </is>
       </c>
       <c r="V6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -9407,7 +9784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10017,6 +10394,108 @@
         </is>
       </c>
       <c r="T6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>16,100</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>13,800</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>10,000 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -10033,7 +10512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH6"/>
+  <dimension ref="A1:AH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11063,6 +11542,178 @@
         </is>
       </c>
       <c r="AH6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4,100 完売</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -11079,7 +11730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11599,6 +12250,93 @@
         </is>
       </c>
       <c r="Q6" t="inlineStr">
+        <is>
+          <t>11,000 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>9,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>10,300</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>11,000 [変動] 完売</t>
         </is>
@@ -11615,7 +12353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12525,6 +13263,158 @@
         </is>
       </c>
       <c r="AD6" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -12541,7 +13431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13061,6 +13951,93 @@
         </is>
       </c>
       <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>5,500 [変動]</t>
         </is>
@@ -14417,7 +15394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14847,6 +15824,78 @@
         </is>
       </c>
       <c r="N6" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
@@ -14863,7 +15912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15107,6 +16156,88 @@
         </is>
       </c>
       <c r="P3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -15123,7 +16254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH6"/>
+  <dimension ref="A1:AH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16153,6 +17284,178 @@
         </is>
       </c>
       <c r="AH6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -16169,7 +17472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16779,6 +18082,108 @@
         </is>
       </c>
       <c r="T6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -16795,7 +18200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17467,6 +18872,118 @@
       <c r="V6" t="inlineStr">
         <is>
           <t>4,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4,600</t>
         </is>
       </c>
     </row>
@@ -17481,7 +18998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17755,6 +19272,98 @@
         </is>
       </c>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>3,400</t>
         </is>
@@ -17771,7 +19380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18681,6 +20290,158 @@
         </is>
       </c>
       <c r="AD6" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -18697,7 +20458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18911,6 +20672,78 @@
         </is>
       </c>
       <c r="N3" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>3,080</t>
         </is>
@@ -18927,7 +20760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19201,6 +21034,98 @@
         </is>
       </c>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>3,200</t>
         </is>
@@ -19217,7 +21142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20127,6 +22052,158 @@
         </is>
       </c>
       <c r="AD6" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -21223,7 +23300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21497,6 +23574,98 @@
         </is>
       </c>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>3,200</t>
         </is>
@@ -21513,7 +23682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21967,6 +24136,158 @@
         </is>
       </c>
       <c r="AD3" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9,800</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -6974,7 +6974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7892,6 +7892,119 @@
       </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9,600 完売</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -7908,7 +8021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8972,6 +9085,158 @@
       <c r="AD7" t="inlineStr">
         <is>
           <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>9,200 完売</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
         </is>
       </c>
     </row>
@@ -8986,7 +9251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9768,6 +10033,118 @@
         </is>
       </c>
       <c r="V7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -9784,7 +10161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10496,6 +10873,108 @@
         </is>
       </c>
       <c r="T7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>16,100</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13,800</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>10,000 完売</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -10512,7 +10991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11714,6 +12193,178 @@
         </is>
       </c>
       <c r="AH7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4,100 完売</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -11730,7 +12381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12337,6 +12988,93 @@
         </is>
       </c>
       <c r="Q7" t="inlineStr">
+        <is>
+          <t>11,000 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>9,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>10,300</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>11,000 [変動] 完売</t>
         </is>
@@ -12353,7 +13091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13415,6 +14153,158 @@
         </is>
       </c>
       <c r="AD7" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -13431,7 +14321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14038,6 +14928,93 @@
         </is>
       </c>
       <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>5,500 [変動]</t>
         </is>
@@ -15394,7 +16371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15896,6 +16873,78 @@
         </is>
       </c>
       <c r="N7" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
@@ -15912,7 +16961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16238,6 +17287,88 @@
         </is>
       </c>
       <c r="P4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -16254,7 +17385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17456,6 +18587,178 @@
         </is>
       </c>
       <c r="AH7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>3,500</t>
         </is>
@@ -17472,7 +18775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18184,6 +19487,108 @@
         </is>
       </c>
       <c r="T7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -18200,7 +19605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18984,6 +20389,118 @@
       <c r="V7" t="inlineStr">
         <is>
           <t>4,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9,300</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4,800</t>
         </is>
       </c>
     </row>
@@ -18998,7 +20515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19364,6 +20881,98 @@
         </is>
       </c>
       <c r="R4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>3,400</t>
         </is>
@@ -19380,7 +20989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20442,6 +22051,158 @@
         </is>
       </c>
       <c r="AD7" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -20458,7 +22219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20744,6 +22505,78 @@
         </is>
       </c>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>3,080</t>
         </is>
@@ -20760,7 +22593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21126,6 +22959,98 @@
         </is>
       </c>
       <c r="R4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>3,200</t>
         </is>
@@ -21142,7 +23067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22204,6 +24129,158 @@
         </is>
       </c>
       <c r="AD7" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -23300,7 +25377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23666,6 +25743,98 @@
         </is>
       </c>
       <c r="R4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>3,200</t>
         </is>
@@ -23682,7 +25851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24288,6 +26457,158 @@
         </is>
       </c>
       <c r="AD4" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9,800</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -6974,7 +6974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8007,6 +8007,119 @@
       <c r="AE9" t="inlineStr">
         <is>
           <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10,100 完売</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>4,000</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9235,6 +9348,158 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,200 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -9251,7 +9516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10145,6 +10410,118 @@
         </is>
       </c>
       <c r="V8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -10161,7 +10538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10192,75 +10569,80 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>メインスタンド指定(M2)ペアシート ベンチ右側</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>メインスタンド指定（Ｍ６） ベンチ左側</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>メインスタンド自由（Ｍ６）</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>メインスタンド指定（Ｍ１） ベンチ右側</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>メインスタンド自由（Ｍ１）</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>エキサイティングシート指定</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ピッチサイドシート指定（Ｂ２）</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ピッチサイドシート指定（Ｂ６）</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>柴田産業Axion指定</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>バックスタンド自由（Ｂ１）</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>バックスタンド自由（Ｂ７）</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ホームゴール裏自由</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ウェルカムシート自由</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>アウェイゴール裏自由</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>車いす席　平面駐車場付</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>車いす席　立体駐車場付</t>
         </is>
@@ -10292,77 +10674,78 @@
           <t>7,700 完売</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>7,100 完売</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>9,500 完売</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>8,100</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>6,400</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -10394,77 +10777,78 @@
           <t>7,600 完売</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>7,200 完売</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>9,800 完売</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>5,400</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>8,100</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>6,500</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>5,100</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -10496,77 +10880,78 @@
           <t>7,600 完売</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>7,200 完売</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>9,800 完売</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>5,400</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>8,100</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>6,500</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>5,100</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -10598,77 +10983,78 @@
           <t>7,700 完売</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>7,200 完売</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>9,900 完売</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>5,400</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>8,100</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>6,500</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>5,100</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>5,900</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -10700,77 +11086,78 @@
           <t>7,700 完売</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>7,200 完売</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>9,900 完売</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>5,400</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>8,100</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>6,500</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>5,100</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>5,900</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -10802,77 +11189,78 @@
           <t>7,800 完売</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>7,400 完売</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>10,000 完売</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>5,600</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>8,100</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>6,500</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>5,900</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -10904,77 +11292,185 @@
           <t>7,800 完売</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>7,400 完売</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>4,600</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>10,000 完売</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>5,600</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>8,100</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>6,500</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>5,200</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>5,900</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>16,100</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13,800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -10991,7 +11487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH8"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11037,14 +11533,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>メインＳ指定南側 メイン下層南側</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>メインＳ指定南側 メイン上層南側</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>メインＳ指定南側 メイン下層南側</t>
-        </is>
-      </c>
       <c r="K1" t="inlineStr">
         <is>
           <t>バックＳ指定北側 バック２階北</t>
@@ -11072,14 +11568,14 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>ホームＡ指定 バック１階南</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>ホームＡ指定 バック１階中央</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ホームＡ指定 バック１階南</t>
-        </is>
-      </c>
       <c r="R1" t="inlineStr">
         <is>
           <t>ホームＡ自由 サイド・バック1階</t>
@@ -11142,14 +11638,14 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>テーブル付ペアシート メイン下層南側</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>テーブル付ペアシート メイン上層南側</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>テーブル付ペアシート メイン下層南側</t>
-        </is>
-      </c>
       <c r="AF1" t="inlineStr">
         <is>
           <t>ＴＨＥＲＭＯＳ パーティーシート 南側</t>
@@ -11163,6 +11659,11 @@
       <c r="AH1" t="inlineStr">
         <is>
           <t>バック車椅子席</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>栗～ンシート メインS指定 南側 メイン上層南側</t>
         </is>
       </c>
     </row>
@@ -11337,6 +11838,7 @@
           <t>3,500</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11509,6 +12011,7 @@
           <t>3,500</t>
         </is>
       </c>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11681,6 +12184,7 @@
           <t>3,500</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11853,6 +12357,7 @@
           <t>3,500</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12025,6 +12530,7 @@
           <t>3,500</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12197,6 +12703,7 @@
           <t>3,500</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12367,6 +12874,184 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>8,000</t>
         </is>
       </c>
     </row>
@@ -12381,7 +13066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13077,6 +13762,93 @@
       <c r="Q8" t="inlineStr">
         <is>
           <t>11,000 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>10,300</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>11,000 完売</t>
         </is>
       </c>
     </row>
@@ -13091,7 +13863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14305,6 +15077,158 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -14321,7 +15245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15017,6 +15941,93 @@
       <c r="Q8" t="inlineStr">
         <is>
           <t>5,500 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>10,400</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,500</t>
         </is>
       </c>
     </row>
@@ -16371,7 +17382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16437,12 +17448,87 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>キングシート／定員8名 【ボックス ２】</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>キングシート／定員8名 【ボックス ８】</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>キングシート／定員8名 【ボックス ６】</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>クイーンシート／定員7名 【ボックス ５】</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>プリンス＆プリンセスシート／定員6名 【ボックス ３】</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>プリンス＆プリンセスシート／定員6名 【ボックス ７】</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>プリンス＆プリンセスシート／定員6名 【ボックス ９】</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>プリンス＆プリンセスシート／定員6名 【ボックス １】</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>カウンターグループシート／定員5名 【グループ １】</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>カウンターグループシート／定員5名 【グループ ２】</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>カウンターグループシート／定員5名 【グループ ４】</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>カウンターグループシート／定員5名 【グループ ３】</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>カウンターペアシート</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>メイン車イス席</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>バック車イス席</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ゼルビアフットサルパーク駐車券１台</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ナック・クリクラ駐車場 駐車券／１台</t>
         </is>
       </c>
     </row>
@@ -16507,16 +17593,31 @@
           <t>2,800</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16579,16 +17680,31 @@
           <t>2,800</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16651,16 +17767,31 @@
           <t>2,800</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16723,16 +17854,31 @@
           <t>2,800</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16795,16 +17941,31 @@
           <t>2,800</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16867,16 +18028,31 @@
           <t>2,800</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>3,080 完売</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16939,14 +18115,176 @@
           <t>2,800</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
         </is>
       </c>
     </row>
@@ -16961,7 +18299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17045,6 +18383,26 @@
           <t>セブン-イレブン最前列シート</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>テーブル付きシート</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ベビーカーファミリーシート バックスタンド</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>バラ席当日引換券</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ベビーカーファミリーシート Ｓスタンド</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17127,6 +18485,10 @@
           <t>5,000</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17209,6 +18571,10 @@
           <t>5,000</t>
         </is>
       </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17291,6 +18657,10 @@
           <t>5,000</t>
         </is>
       </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17371,6 +18741,112 @@
       <c r="P5" t="inlineStr">
         <is>
           <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -17385,7 +18861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH8"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17431,14 +18907,14 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>メインＳ指定南側 メイン下層南側</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>メインＳ指定南側 メイン上層南側</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>メインＳ指定南側 メイン下層南側</t>
-        </is>
-      </c>
       <c r="K1" t="inlineStr">
         <is>
           <t>バックＳ指定北側 バック２階北</t>
@@ -17466,14 +18942,14 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>ホームＡ指定 バック１階南</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>ホームＡ指定 バック１階中央</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>ホームＡ指定 バック１階南</t>
-        </is>
-      </c>
       <c r="R1" t="inlineStr">
         <is>
           <t>ホームＡ自由 サイド・バック1階</t>
@@ -17536,14 +19012,14 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>テーブル付ペアシート メイン下層南側</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>テーブル付ペアシート メイン上層南側</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>テーブル付ペアシート メイン下層南側</t>
-        </is>
-      </c>
       <c r="AF1" t="inlineStr">
         <is>
           <t>ＴＨＥＲＭＯＳ パーティーシート 南側</t>
@@ -17557,6 +19033,11 @@
       <c r="AH1" t="inlineStr">
         <is>
           <t>バック車椅子席</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>水曜日のフロンタウンシートSA指定 ゴール裏２階南</t>
         </is>
       </c>
     </row>
@@ -17731,6 +19212,7 @@
           <t>3,500</t>
         </is>
       </c>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17903,6 +19385,7 @@
           <t>3,500</t>
         </is>
       </c>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18075,6 +19558,7 @@
           <t>3,500</t>
         </is>
       </c>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18247,6 +19731,7 @@
           <t>3,500</t>
         </is>
       </c>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18419,6 +19904,7 @@
           <t>3,500</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18591,6 +20077,7 @@
           <t>3,500</t>
         </is>
       </c>
+      <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18761,6 +20248,184 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>6,000</t>
         </is>
       </c>
     </row>
@@ -18775,7 +20440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18806,75 +20471,80 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>メインスタンド指定(M2)ペアシート ベンチ右側</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>メインスタンド指定（Ｍ６） ベンチ左側</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>メインスタンド自由（Ｍ６）</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>メインスタンド指定（Ｍ１） ベンチ右側</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>メインスタンド自由（Ｍ１）</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>エキサイティングシート指定</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ピッチサイドシート指定（Ｂ２）</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ピッチサイドシート指定（Ｂ６）</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>柴田産業Axion指定</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>バックスタンド自由（Ｂ１）</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>バックスタンド自由（Ｂ７）</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ホームゴール裏自由</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ウェルカムシート自由</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>アウェイゴール裏自由</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>車いす席　平面駐車場付</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>車いす席　立体駐車場付</t>
         </is>
@@ -18906,77 +20576,78 @@
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
         <is>
           <t>5,500 完売</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -19008,77 +20679,78 @@
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>5,500 完売</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -19110,77 +20782,78 @@
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>5,500 完売</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -19212,77 +20885,78 @@
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>5,500 完売</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -19314,77 +20988,78 @@
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>5,500 完売</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -19416,77 +21091,78 @@
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>5,500 完売</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -19518,77 +21194,185 @@
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>5,500 完売</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>6,000 完売</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>4,500</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>2,000</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -19605,7 +21389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20501,6 +22285,118 @@
       <c r="V8" t="inlineStr">
         <is>
           <t>4,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>5,000</t>
         </is>
       </c>
     </row>
@@ -20515,7 +22411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20601,12 +22497,32 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>アウェイ指定席</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>セブン-イレブン最前列シート</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>アウェイ指定席</t>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>バラ席当日引換券</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ベビーカーファミリーシート Ｓスタンド</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>テーブル付きシート</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ベビーカーファミリーシート バックスタンド</t>
         </is>
       </c>
     </row>
@@ -20693,14 +22609,18 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>5,200</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20785,14 +22705,18 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>5,200</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -20877,14 +22801,18 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>5,200</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -20969,12 +22897,128 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>5,200</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>3,400</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
         </is>
       </c>
     </row>
@@ -20989,7 +23033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22203,6 +24247,158 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -22219,7 +24415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22285,12 +24481,87 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>キングシート／定員8名 【ボックス ２】</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>キングシート／定員8名 【ボックス ８】</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>キングシート／定員8名 【ボックス ６】</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>クイーンシート／定員7名 【ボックス ５】</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>プリンス＆プリンセスシート／定員6名 【ボックス ３】</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>プリンス＆プリンセスシート／定員6名 【ボックス ７】</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>プリンス＆プリンセスシート／定員6名 【ボックス ９】</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>プリンス＆プリンセスシート／定員6名 【ボックス １】</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>カウンターグループシート／定員5名 【グループ １】</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>カウンターグループシート／定員5名 【グループ ２】</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>カウンターグループシート／定員5名 【グループ ４】</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>カウンターグループシート／定員5名 【グループ ３】</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>カウンターペアシート</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>メイン車イス席</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>バック車イス席</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ゼルビアフットサルパーク駐車券１台</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ナック・クリクラ駐車場 駐車券／１台</t>
         </is>
       </c>
     </row>
@@ -22355,16 +24626,31 @@
           <t>3,700 完売</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>3,080</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22427,16 +24713,31 @@
           <t>3,700 完売</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>3,080</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22499,16 +24800,31 @@
           <t>3,700 完売</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>3,080</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22571,14 +24887,176 @@
           <t>3,700 完売</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
         </is>
       </c>
     </row>
@@ -22593,7 +25071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22679,12 +25157,32 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>アウェイ指定席</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>セブン-イレブン最前列シート</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>アウェイ指定席</t>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>バラ席当日引換券</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ベビーカーファミリーシート Ｓスタンド</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>テーブル付きシート</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ベビーカーファミリーシート バックスタンド</t>
         </is>
       </c>
     </row>
@@ -22771,14 +25269,18 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22863,14 +25365,18 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22955,14 +25461,18 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23047,12 +25557,128 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>3,200</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -23067,7 +25693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24281,6 +26907,158 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -25377,7 +28155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25463,12 +28241,32 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>アウェイ指定席</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
           <t>セブン-イレブン最前列シート</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>アウェイ指定席</t>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>バラ席当日引換券</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ベビーカーファミリーシート Ｓスタンド</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>テーブル付きシート</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ベビーカーファミリーシート バックスタンド</t>
         </is>
       </c>
     </row>
@@ -25555,14 +28353,18 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25647,14 +28449,18 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -25739,14 +28545,18 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -25831,12 +28641,128 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>3,200</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
         </is>
       </c>
     </row>
@@ -25851,7 +28777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26609,6 +29535,158 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-09 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13,500 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,800</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -8013,7 +8013,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-09 06:00</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6,800</t>
+          <t>6,800 完売</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -9356,7 +9356,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 06:00</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8,200</t>
+          <t>8,200 完売</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7,300 完売</t>
+          <t>7,600 完売</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6,300</t>
+          <t>6,600</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -9416,17 +9416,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5,500 完売</t>
+          <t>5,500</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>5,100</t>
+          <t>5,300</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>6,000 完売</t>
+          <t>5,700 完売</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>4,400 完売</t>
+          <t>4,400</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -9451,37 +9451,37 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>4,400 完売</t>
+          <t>4,400</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
           <t>3,100</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>3,200 完売</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2,700</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>3,100</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>3,500</t>
+          <t>3,500 完売</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -10418,7 +10418,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11372,12 +11372,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>16,100</t>
+          <t>16,200</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -11387,12 +11387,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>7,300</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>8,100</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10,100</t>
+          <t>10,700</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5,200</t>
+          <t>5,500</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3,300</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -12881,7 +12881,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -12921,12 +12921,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6,900 完売</t>
+          <t>6,700 完売</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>6,700</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>5,000 完売</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -12981,12 +12981,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>5,400</t>
+          <t>5,200</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -13768,7 +13768,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -15085,7 +15085,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 06:00</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6,500 完売</t>
+          <t>6,700 完売</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5,500</t>
+          <t>5,700</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -15145,12 +15145,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5,200</t>
+          <t>5,400</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3,900</t>
+          <t>4,000</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -15185,32 +15185,32 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>3,100</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2,600</t>
+          <t>2,700</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
           <t>3,300</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3,300</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>3,500</t>
+          <t>3,600</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3,000</t>
+          <t>3,100</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -15220,7 +15220,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>3,700</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -15947,7 +15947,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -18144,7 +18144,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -18751,7 +18751,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -20255,7 +20255,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:40</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -21274,7 +21274,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -22291,7 +22291,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -22301,32 +22301,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>6,100</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6,600</t>
+          <t>6,700</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6,200</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>5,500</t>
+          <t>5,300</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -22351,44 +22351,44 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>4,100</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>4,600</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>4,500</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>4,200</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>2,700</t>
@@ -22396,7 +22396,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>5,300</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -24255,7 +24255,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -24916,7 +24916,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -24946,7 +24946,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5,300</t>
+          <t>5,300 完売</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3,500 完売</t>
+          <t>3,500</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -25016,7 +25016,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>5,500</t>
+          <t>5,500 完売</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -25573,7 +25573,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -26915,7 +26915,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:39</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -26940,12 +26940,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7,100</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6,100</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -26970,7 +26970,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3,500</t>
+          <t>3,600</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -26990,7 +26990,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>4,700</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -27005,7 +27005,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -27030,12 +27030,12 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2,400</t>
+          <t>2,500</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2,900</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -28657,7 +28657,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -29543,67 +29543,67 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-09 06:01</t>
+          <t>2026-10-09 16:40</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13,500 完売</t>
+          <t>13,600 完売</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12,500</t>
+          <t>12,600</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9,800</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8,800</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8,600</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>7,600</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>7,000</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>7,400</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -29613,12 +29613,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>5,400</t>
+          <t>5,600 完売</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>4,300</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -8134,7 +8134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9500,6 +9500,158 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,200 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,100 完売</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -9516,7 +9668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10522,6 +10674,118 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>4,000</t>
         </is>
@@ -10538,7 +10802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11471,6 +11735,113 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>16,200</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13,800</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10,700</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -11487,7 +11858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13050,6 +13421,183 @@
         </is>
       </c>
       <c r="AI9" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -13066,7 +13614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13847,6 +14395,93 @@
         </is>
       </c>
       <c r="Q9" t="inlineStr">
+        <is>
+          <t>11,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>10,300</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>11,000 完売</t>
         </is>
@@ -13863,7 +14498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15229,6 +15864,158 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -15245,7 +16032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16026,6 +16813,93 @@
         </is>
       </c>
       <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10,400</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
@@ -17382,7 +18256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18288,6 +19162,153 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18299,7 +19320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18845,6 +19866,108 @@
         </is>
       </c>
       <c r="T6" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -18861,7 +19984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20424,6 +21547,183 @@
         </is>
       </c>
       <c r="AI9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
@@ -20440,7 +21740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21373,6 +22673,113 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -21389,7 +22796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22395,6 +23802,118 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -22411,7 +23930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23017,6 +24536,118 @@
         </is>
       </c>
       <c r="V6" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -23033,7 +24664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24399,6 +26030,158 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -24415,7 +26198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25060,6 +26843,153 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25071,7 +27001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25677,6 +27607,118 @@
         </is>
       </c>
       <c r="V6" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -25693,7 +27735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27059,6 +29101,158 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -28155,7 +30349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28761,6 +30955,118 @@
         </is>
       </c>
       <c r="V6" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3,200 完売</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -28777,7 +31083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29687,6 +31993,158 @@
         </is>
       </c>
       <c r="AD6" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13,600 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -11858,7 +11858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13598,6 +13598,183 @@
         </is>
       </c>
       <c r="AI10" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -13614,7 +13791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14484,6 +14661,93 @@
       <c r="Q10" t="inlineStr">
         <is>
           <t>11,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>9,250</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>9,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>10,300 完売</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>11,000 [変動] 完売</t>
         </is>
       </c>
     </row>
@@ -14498,7 +14762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16016,6 +16280,158 @@
         </is>
       </c>
       <c r="AD10" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -16032,7 +16448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16902,6 +17318,93 @@
       <c r="Q10" t="inlineStr">
         <is>
           <t>5,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>10,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5,500 [変動]</t>
         </is>
       </c>
     </row>
@@ -18256,7 +18759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19309,6 +19812,153 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19320,7 +19970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19968,6 +20618,108 @@
         </is>
       </c>
       <c r="T7" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -19984,7 +20736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21724,6 +22476,183 @@
         </is>
       </c>
       <c r="AI10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
@@ -21740,7 +22669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22780,6 +23709,113 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -22796,7 +23832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23914,6 +24950,118 @@
         </is>
       </c>
       <c r="V10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -23930,7 +25078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24648,6 +25796,118 @@
         </is>
       </c>
       <c r="V7" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -24664,7 +25924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26182,6 +27442,158 @@
         </is>
       </c>
       <c r="AD10" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -26198,7 +27610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26990,6 +28402,153 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27001,7 +28560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27719,6 +29278,118 @@
         </is>
       </c>
       <c r="V7" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -27735,7 +29406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29253,6 +30924,158 @@
         </is>
       </c>
       <c r="AD10" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -30349,7 +32172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31069,6 +32892,118 @@
       <c r="V7" t="inlineStr">
         <is>
           <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -31083,7 +33018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32145,6 +34080,158 @@
         </is>
       </c>
       <c r="AD7" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13,600 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -14762,7 +14762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16432,6 +16432,158 @@
         </is>
       </c>
       <c r="AD11" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:00</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -16448,7 +16600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17405,6 +17557,93 @@
       <c r="Q11" t="inlineStr">
         <is>
           <t>5,500 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5,500 [変動] 完売</t>
         </is>
       </c>
     </row>
@@ -18759,7 +18998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19959,6 +20198,149 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19970,7 +20352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20720,6 +21102,108 @@
         </is>
       </c>
       <c r="T8" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -20736,7 +21220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22653,6 +23137,183 @@
         </is>
       </c>
       <c r="AI11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
@@ -22669,7 +23330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23816,6 +24477,113 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -23832,7 +24600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25062,6 +25830,118 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -25078,7 +25958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25908,6 +26788,118 @@
         </is>
       </c>
       <c r="V8" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -25924,7 +26916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27594,6 +28586,158 @@
         </is>
       </c>
       <c r="AD11" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -27610,7 +28754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28549,6 +29693,153 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28560,7 +29851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29390,6 +30681,118 @@
         </is>
       </c>
       <c r="V8" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -29406,7 +30809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31076,6 +32479,158 @@
         </is>
       </c>
       <c r="AD11" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -32172,7 +33727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33002,6 +34557,118 @@
         </is>
       </c>
       <c r="V8" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -33018,7 +34685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34232,6 +35899,158 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>14,200 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -14762,7 +14762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16584,6 +16584,158 @@
         </is>
       </c>
       <c r="AD12" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8,800 完売</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4,700 完売</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -16600,7 +16752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17642,6 +17794,93 @@
         </is>
       </c>
       <c r="Q12" t="inlineStr">
+        <is>
+          <t>5,500 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>5,500 [変動] 完売</t>
         </is>
@@ -18998,7 +19237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20341,6 +20580,149 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20352,7 +20734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21204,6 +21586,108 @@
         </is>
       </c>
       <c r="T9" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -21220,7 +21704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI12"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23314,6 +23798,183 @@
         </is>
       </c>
       <c r="AI12" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
@@ -23330,7 +23991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24584,6 +25245,113 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -24600,7 +25368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25942,6 +26710,118 @@
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -25958,7 +26838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26900,6 +27780,118 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -26916,7 +27908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28738,6 +29730,158 @@
         </is>
       </c>
       <c r="AD12" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -28754,7 +29898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29840,6 +30984,153 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29851,7 +31142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30793,6 +32084,118 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -30809,7 +32212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32631,6 +34034,158 @@
         </is>
       </c>
       <c r="AD12" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -33727,7 +35282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34669,6 +36224,118 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -34685,7 +36352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36051,6 +37718,158 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -47,8 +47,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="G大阪-C大阪_1108" sheetId="38" state="visible" r:id="rId38"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="町田-広島_1108" sheetId="39" state="visible" r:id="rId39"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C大阪-FC東京_1121" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名古屋-福岡_1129" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C大阪-水戸_1205" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="G大阪-岡山_1121" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名古屋-福岡_1129" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C大阪-水戸_1205" sheetId="43" state="visible" r:id="rId43"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14773,7 +14774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD14"/>
+  <dimension ref="A1:AE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14927,6 +14928,11 @@
           <t>バリュープライスシートBホーム</t>
         </is>
       </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートＣホーム</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15079,6 +15085,7 @@
           <t>2,500</t>
         </is>
       </c>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15231,6 +15238,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15383,6 +15391,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15535,6 +15544,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15687,6 +15697,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15839,6 +15850,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15991,6 +16003,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16143,6 +16156,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16295,6 +16309,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16447,6 +16462,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16599,6 +16615,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16751,6 +16768,7 @@
           <t>2,500 完売</t>
         </is>
       </c>
+      <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16901,6 +16919,164 @@
       <c r="AD14" t="inlineStr">
         <is>
           <t>2,500 完売</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8,800 完売</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>3,000 完売</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
         </is>
       </c>
     </row>
@@ -16915,7 +17091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18131,6 +18307,93 @@
         </is>
       </c>
       <c r="Q14" t="inlineStr">
+        <is>
+          <t>5,500 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>5,500 [変動] 完売</t>
         </is>
@@ -19487,7 +19750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21116,6 +21379,149 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21127,7 +21533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22183,6 +22589,108 @@
         </is>
       </c>
       <c r="T11" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -22199,7 +22707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI14"/>
+  <dimension ref="A1:AI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24647,6 +25155,183 @@
         </is>
       </c>
       <c r="AI14" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
@@ -24663,7 +25348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26131,6 +26816,113 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -26147,7 +26939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27713,6 +28505,118 @@
         </is>
       </c>
       <c r="V14" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -27729,7 +28633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28031,6 +28935,158 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>15,300</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>15,000 完売</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -28047,7 +29103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28229,6 +29285,98 @@
         </is>
       </c>
       <c r="R2" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>11,100 [変動]</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>4,200 [変動]</t>
         </is>
@@ -28245,7 +29393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29411,6 +30559,118 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -29427,7 +30687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29639,6 +30899,113 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -29655,7 +31022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD14"/>
+  <dimension ref="A1:AD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31781,6 +33148,158 @@
         </is>
       </c>
       <c r="AD14" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -32877,7 +34396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33229,6 +34748,183 @@
         </is>
       </c>
       <c r="AI2" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -33245,7 +34941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33469,6 +35165,118 @@
       <c r="V2" t="inlineStr">
         <is>
           <t>4,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>4,800</t>
         </is>
       </c>
     </row>
@@ -33483,7 +35291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ2"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33917,6 +35725,223 @@
       <c r="AQ2" t="inlineStr">
         <is>
           <t>4,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>4,800</t>
         </is>
       </c>
     </row>
@@ -33931,7 +35956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35311,6 +37336,153 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35322,7 +37494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35724,6 +37896,208 @@
         </is>
       </c>
       <c r="AN2" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
         <is>
           <t>4,100</t>
         </is>
@@ -35740,7 +38114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36906,6 +39280,118 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -36922,7 +39408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37244,6 +39730,168 @@
         </is>
       </c>
       <c r="AF2" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
@@ -37260,7 +39908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37462,6 +40110,108 @@
         </is>
       </c>
       <c r="T2" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>15,300</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>13,100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -37478,7 +40228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37780,6 +40530,158 @@
         </is>
       </c>
       <c r="AD2" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>19,900 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10,300 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>9,000 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>10,600 完売</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>12,600 完売</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>9,500</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>19,800</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>5,300 完売</t>
         </is>
@@ -37796,7 +40698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38088,6 +40990,153 @@
         </is>
       </c>
       <c r="AC2" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,500 完売</t>
         </is>
@@ -40054,7 +43103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD14"/>
+  <dimension ref="A1:AD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42180,6 +45229,158 @@
         </is>
       </c>
       <c r="AD14" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -42196,7 +45397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42207,1163 +45408,329 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ロイヤルシート</t>
+          <t>エキサイティングシート</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ＳＳ指定席 北側</t>
+          <t>カテゴリー１ＦＶ</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ＳＳ指定席 南側</t>
+          <t>カテゴリー１</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Ｓ指定席</t>
+          <t>カテゴリー２ＦＶ</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Ａ指定席 南側</t>
+          <t>カテゴリー２</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Ａ指定席 北側</t>
+          <t>カテゴリー３ バック側</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Ｂ指定席</t>
+          <t>カテゴリー３ メイン側</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Ｃ指定席</t>
+          <t>カテゴリー４ＦＶ</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>メイン３階指定席</t>
+          <t>カテゴリー４ミックスＦＶ</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>バック３階指定席</t>
+          <t>カテゴリー４</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>メイン４階指定席</t>
+          <t>カテゴリー４ミックス</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>バック４階指定席</t>
+          <t>カテゴリー４テーブルシート</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>ゴール裏指定席１階北側</t>
+          <t>カテゴリー５ＦＶ</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>ゴール裏指定席２階北側</t>
+          <t>カテゴリー５</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>ゴール裏指定席１階南側</t>
+          <t>カテゴリー６指定席ＦＶ</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>アウェイ指定席</t>
+          <t>カテゴリー６指定席</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>セブン-イレブン最前列シート</t>
+          <t>カテゴリー６自由席</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>バラ席当日引換券</t>
+          <t>ガンバサポーターシート</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>ベビーカーファミリーシート Ｓスタンド</t>
+          <t>車椅子席 メイン側</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>テーブル付きシート</t>
+          <t>車椅子ミックス席 メイン側</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>ベビーカーファミリーシート バックスタンド</t>
+          <t>ユニバーサル席 バック側</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ビジター指定席</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>モリタにこにこ家族ラウンジ</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>くくるラウンジ（バック側）</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>カジュアルラウンジ（ＶＣ２０）</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>モフレムもぐもぐチケット</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>モフレムラウンジ（ＶＡ１）</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>カテゴリー４ミックス視界制限席</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>カテゴリー４視界制限席</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>カテゴリー５視界制限席</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>モフレムルームＢ</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>モフレムルームＡ</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05 21:25</t>
+          <t>2026-10-15 06:02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>15,800</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6,400 完売</t>
+          <t>6,600</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6,400 完売</t>
+          <t>6,100</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>5,800</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,900 完売</t>
+          <t>5,300</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3,900 完売</t>
+          <t>4,800</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>3,900</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>3,400</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>3,000 完売</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>13,700 完売</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13,700 完売</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16,000 完売</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>3,400</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-06 06:02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>6,400 完売</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>6,400 完売</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3,900 完売</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>3,900 完売</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-07 06:01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>6,400 完売</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>6,400 完売</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3,900 完売</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3,900 完売</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-08 06:01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>6,400 完売</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>6,400 完売</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3,900 完売</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>3,900 完売</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-09 16:40</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>3,200 完売</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>20,000 完売</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>20,000 完売</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-10 06:01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>3,200 完売</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>20,000 完売</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>20,000 完売</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-11 06:01</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-12 06:01</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-13 06:01</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:01</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>20,000</t>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
         </is>
       </c>
     </row>
@@ -43378,7 +45745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43389,147 +45756,107 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>エキサイティングシート(ホーム)前方</t>
+          <t>ロイヤルシート</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>エキサイティングシート（ホーム）</t>
+          <t>ＳＳ指定席 北側</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ホームメイン北SS指定席前方</t>
+          <t>ＳＳ指定席 南側</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ホームメイン北SS指定席</t>
+          <t>Ｓ指定席</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ホームメイン南SS指定席前方</t>
+          <t>Ａ指定席 南側</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>ホームメイン南SS指定席</t>
+          <t>Ａ指定席 北側</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>ホームメイン北S指定席前方</t>
+          <t>Ｂ指定席</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>ホームメイン北S指定席</t>
+          <t>Ｃ指定席</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ミックスメイン南S指定席前方</t>
+          <t>メイン３階指定席</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>ミックスメイン南S指定席</t>
+          <t>バック３階指定席</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>ホームメインセンターA指定席</t>
+          <t>メイン４階指定席</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>ホームメイン北A指定席</t>
+          <t>バック４階指定席</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>ホームメイン南A指定席</t>
+          <t>ゴール裏指定席１階北側</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>バックセンターシート下段ホーム</t>
+          <t>ゴール裏指定席２階北側</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>バックセンターシート上段ホーム</t>
+          <t>ゴール裏指定席１階南側</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>ホームバック北A指定席下段</t>
+          <t>アウェイ指定席</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>ホームバック北A指定席上段</t>
+          <t>セブン-イレブン最前列シート</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>ホームバック南A指定席下段</t>
+          <t>バラ席当日引換券</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>ホームバック南A指定席上段</t>
+          <t>ベビーカーファミリーシート Ｓスタンド</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>ホームバック北B指定席下段</t>
+          <t>テーブル付きシート</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>ホームバック北B指定席上段</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>ホームバック南B指定席下段</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>ホームバック南B指定席上段</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>ホームサポーター指定席</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>ホームサポーター自由席</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>ホーム南スタンド自由席</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>ビジターサポーター指定席</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>バリュープライスシートAホーム</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>バリュープライスシートBホーム</t>
+          <t>ベビーカーファミリーシート バックスタンド</t>
         </is>
       </c>
     </row>
@@ -43541,149 +45868,93 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13,100 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12,100</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9,400</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8,400</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8,500</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7,100</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>6,100</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5,600</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>4,700</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>5,200</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>3,500 完売</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>2,500</t>
-        </is>
-      </c>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -43693,149 +45964,93 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13,100 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12,100</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9,400</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8,400</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8,500</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7,100</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>6,100</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5,600</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4,700</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>5,200</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>3,500 完売</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>2,500</t>
-        </is>
-      </c>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -43845,149 +46060,93 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13,500</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12,500</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9,800</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8,800</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8,600</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7,600</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7,400</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>6,400</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>5,000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>5,400</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>4,300</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>3,500 完売</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>2,500</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -43997,149 +46156,93 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13,500</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12,500</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9,800</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8,800</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8,600</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7,600</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7,400</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>6,400</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>5,000</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>5,400</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>4,300</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>3,500 完売</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>2,500</t>
-        </is>
-      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -44149,147 +46252,107 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13,600 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12,600</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>5,600 完売</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>3,200 完売</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>5,800</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>20,000 完売</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>7,800</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>2,500</t>
+          <t>20,000 完売</t>
         </is>
       </c>
     </row>
@@ -44301,147 +46364,107 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13,600 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12,600</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>6,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>5,600 完売</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>3,200 完売</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>5,800</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>20,000 完売</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>7,800</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>2,500</t>
+          <t>20,000 完売</t>
         </is>
       </c>
     </row>
@@ -44453,147 +46476,107 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13,600 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12,600</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>6,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>5,600 完売</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>5,800</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>7,800</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>2,500</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -44605,147 +46588,107 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14,200 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13,200</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9,200</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8,200</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5,100</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>5,600 完売</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>5,800</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>7,800</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2,500</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -44757,147 +46700,107 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14,500 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13,500</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9,600</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8,600</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>7,800</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>6,800</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>5,300</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4,800</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>5,600 完売</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2,900</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>2,500</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -44909,9 +46812,1767 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート(ホーム)前方</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート（ホーム）</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席前方</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席前方</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席前方</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席前方</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ホームメインセンターA指定席</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ホームメイン北A指定席</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ホームメイン南A指定席</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>バックセンターシート下段ホーム</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>バックセンターシート上段ホーム</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席下段</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席上段</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席下段</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席上段</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席下段</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席上段</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席下段</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席上段</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ホームサポーター指定席</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ホームサポーター自由席</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ホーム南スタンド自由席</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ビジターサポーター指定席</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートAホーム</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートBホーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:25</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13,100 完売</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13,100 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9,800</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9,800</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:40</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13,600 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13,600 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13,600 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>14,200 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>14,500 完売</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>13,500</t>
@@ -45048,6 +48709,158 @@
         </is>
       </c>
       <c r="AD11" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9,700</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -14774,7 +14774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE15"/>
+  <dimension ref="A1:AE16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17077,6 +17077,163 @@
       <c r="AE15" t="inlineStr">
         <is>
           <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>8,800 完売</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>3,100 完売</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>1,500</t>
         </is>
       </c>
     </row>
@@ -17091,7 +17248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18394,6 +18551,93 @@
         </is>
       </c>
       <c r="Q15" t="inlineStr">
+        <is>
+          <t>5,500 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>10,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>8,100 [変動]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>5,500 [変動] 完売</t>
         </is>
@@ -19750,7 +19994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21522,6 +21766,149 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21533,7 +21920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22691,6 +23078,108 @@
         </is>
       </c>
       <c r="T12" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -22707,7 +23196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25332,6 +25821,183 @@
         </is>
       </c>
       <c r="AI15" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
@@ -25348,7 +26014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26923,6 +27589,113 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -26939,7 +27712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28617,6 +29390,118 @@
         </is>
       </c>
       <c r="V15" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -28633,7 +29518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29087,6 +29972,158 @@
         </is>
       </c>
       <c r="AD3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>15,300</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>15,000 完売</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -29103,7 +30140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29377,6 +30414,98 @@
         </is>
       </c>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>10,900 [変動]</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>4,200 [変動]</t>
         </is>
@@ -29393,7 +30522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30671,6 +31800,118 @@
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -30687,7 +31928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31006,6 +32247,113 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -31022,7 +32370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AD16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33300,6 +34648,158 @@
         </is>
       </c>
       <c r="AD15" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:00</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -34396,7 +35896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI3"/>
+  <dimension ref="A1:AI4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34925,6 +36425,183 @@
         </is>
       </c>
       <c r="AI3" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -34941,7 +36618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35277,6 +36954,118 @@
       <c r="V3" t="inlineStr">
         <is>
           <t>4,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>5,000</t>
         </is>
       </c>
     </row>
@@ -35291,7 +37080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35940,6 +37729,223 @@
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
@@ -35956,7 +37962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37483,6 +39489,153 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -37494,7 +39647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN3"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38098,6 +40251,208 @@
         </is>
       </c>
       <c r="AN3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
         <is>
           <t>4,100</t>
         </is>
@@ -38114,7 +40469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39392,6 +41747,118 @@
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -39408,7 +41875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39892,6 +42359,168 @@
         </is>
       </c>
       <c r="AF3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
@@ -39908,7 +42537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40212,6 +42841,108 @@
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>15,100</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12,800</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -40228,7 +42959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40684,6 +43415,158 @@
       <c r="AD3" t="inlineStr">
         <is>
           <t>5,300 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>19,900 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10,300 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>9,000 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>11,600 完売</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>9,500</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>19,800</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>5,300</t>
         </is>
       </c>
     </row>
@@ -40698,7 +43581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41137,6 +44020,153 @@
         </is>
       </c>
       <c r="AC3" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,500 完売</t>
         </is>
@@ -43103,7 +46133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AD16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45381,6 +48411,158 @@
         </is>
       </c>
       <c r="AD15" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -45397,7 +48579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45729,6 +48911,173 @@
         </is>
       </c>
       <c r="AG2" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3,000 完売</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>13,700 完売</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13,700 完売</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16,000 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>33,000 完売</t>
         </is>
@@ -45745,7 +49094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47023,6 +50372,118 @@
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -47039,7 +50500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48861,6 +52322,158 @@
         </is>
       </c>
       <c r="AD12" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -48,8 +48,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="町田-広島_1108" sheetId="39" state="visible" r:id="rId39"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C大阪-FC東京_1121" sheetId="40" state="visible" r:id="rId40"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="G大阪-岡山_1121" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名古屋-福岡_1129" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C大阪-水戸_1205" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="横浜FM-FC東京_1129" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名古屋-福岡_1129" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C大阪-水戸_1205" sheetId="44" state="visible" r:id="rId44"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14774,7 +14775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE16"/>
+  <dimension ref="A1:AE17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17234,6 +17235,163 @@
       <c r="AE16" t="inlineStr">
         <is>
           <t>1,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:00</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>9,800 完売</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
         </is>
       </c>
     </row>
@@ -17248,7 +17406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18638,6 +18796,93 @@
         </is>
       </c>
       <c r="Q16" t="inlineStr">
+        <is>
+          <t>5,500 [変動] 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>9,250</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>10,400 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8,900 [変動]</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>8,300 [変動]</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>7,600 [変動]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>4,100 完売</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>14,300 完売</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>12,000 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>5,500 [変動] 完売</t>
         </is>
@@ -19994,7 +20239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21909,6 +22154,149 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21920,7 +22308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23180,6 +23568,108 @@
         </is>
       </c>
       <c r="T13" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -23196,7 +23686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI16"/>
+  <dimension ref="A1:AI17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25998,6 +26488,183 @@
         </is>
       </c>
       <c r="AI16" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
@@ -26014,7 +26681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27696,6 +28363,113 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -27712,7 +28486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29502,6 +30276,118 @@
         </is>
       </c>
       <c r="V16" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -29518,7 +30404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30124,6 +31010,158 @@
         </is>
       </c>
       <c r="AD4" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15,300</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>15,000 完売</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -30140,7 +31178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30506,6 +31544,98 @@
         </is>
       </c>
       <c r="R4" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>10,900 [変動]</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>4,200 [変動]</t>
         </is>
@@ -30522,7 +31652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31912,6 +33042,118 @@
         </is>
       </c>
       <c r="V13" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -31928,7 +33170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32356,6 +33598,113 @@
       <c r="U4" t="inlineStr">
         <is>
           <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>5,400</t>
         </is>
       </c>
     </row>
@@ -32370,7 +33719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:AD17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34800,6 +36149,158 @@
         </is>
       </c>
       <c r="AD16" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -35896,7 +37397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36602,6 +38103,183 @@
         </is>
       </c>
       <c r="AI4" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -36618,7 +38296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37066,6 +38744,118 @@
       <c r="V4" t="inlineStr">
         <is>
           <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>5,300</t>
         </is>
       </c>
     </row>
@@ -37080,7 +38870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37946,6 +39736,223 @@
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
@@ -37962,7 +39969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39636,6 +41643,153 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -39647,7 +41801,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN4"/>
+  <dimension ref="A1:AN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40453,6 +42607,208 @@
         </is>
       </c>
       <c r="AN4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
         <is>
           <t>4,100</t>
         </is>
@@ -40469,7 +42825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41859,6 +44215,118 @@
         </is>
       </c>
       <c r="V13" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -41875,7 +44343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF4"/>
+  <dimension ref="A1:AF5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42521,6 +44989,168 @@
         </is>
       </c>
       <c r="AF4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
@@ -42537,7 +45167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42943,6 +45573,108 @@
         </is>
       </c>
       <c r="T4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15,400</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,900</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -42959,7 +45691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43565,6 +46297,158 @@
         </is>
       </c>
       <c r="AD4" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>19,900 完売</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10,300 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>9,000 完売</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>12,700 完売</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>15,100 完売</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>9,500</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>19,800</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -43581,7 +46465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44167,6 +47051,153 @@
         </is>
       </c>
       <c r="AC4" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,500 完売</t>
         </is>
@@ -46133,7 +49164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:AD17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48563,6 +51594,158 @@
         </is>
       </c>
       <c r="AD16" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -48579,7 +51762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49078,6 +52261,173 @@
         </is>
       </c>
       <c r="AG3" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>15,800 完売</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>4,500 完売</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,100 完売</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3,000 完売</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>13,700 完売</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13,700 完売</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16,000 完売</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>33,000 完売</t>
         </is>
@@ -49094,7 +52444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:AP2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49105,1387 +52455,419 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ロイヤルシート</t>
+          <t>カジュアルラウンジ付チケット １階ホームエリア</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ＳＳ指定席 北側</t>
+          <t>デラックスシート ２階ミックスエリア</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ＳＳ指定席 南側</t>
+          <t>デラックスシート ２階ホームエリア</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Ｓ指定席</t>
+          <t>カウンターシート２ ２階ミックスエリア</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Ａ指定席 南側</t>
+          <t>カウンターシート４ ２階ミックスエリア</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Ａ指定席 北側</t>
+          <t>カウンターシート４ ２階ホームエリア</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Ｂ指定席</t>
+          <t>ペアシート ２階ミックスエリア</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Ｃ指定席</t>
+          <t>ペアシート ２階ホームエリア</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>メイン３階指定席</t>
+          <t>メインＳＳＳ １階ミックスエリア</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>バック３階指定席</t>
+          <t>メインＳＳＳ １階ホームエリア</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>メイン４階指定席</t>
+          <t>メインＳＳ １階ホームエリア</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>バック４階指定席</t>
+          <t>メインＳＳ １階ミックスエリア</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>ゴール裏指定席１階北側</t>
+          <t>メインＳＳ ２階ホームエリア</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>ゴール裏指定席２階北側</t>
+          <t>メインＳＳ ２階ミックスエリア</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>ゴール裏指定席１階南側</t>
+          <t>メインＳＡ １階ホームエリア</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>アウェイ指定席</t>
+          <t>メインＳＡ １階ミックスエリア</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>セブン-イレブン最前列シート</t>
+          <t>メインＳＡ ２階ミックスエリア</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>バラ席当日引換券</t>
+          <t>メインＳＡ ２階ホームエリア</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>ベビーカーファミリーシート Ｓスタンド</t>
+          <t>バックＳＢ １階ホームエリア</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>テーブル付きシート</t>
+          <t>バックＳＢ ２階ホームエリア</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>ベビーカーファミリーシート バックスタンド</t>
+          <t>バックＳＣ １階ホームエリア</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>バックアッパー ２階ホームエリア</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>メインサイド １階ミックスエリア</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>メインサイド １階ホームエリア</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>メインサイド ２階ミックスエリア</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>メインサイド ２階ホームエリア</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>バックサイド １階ホームエリア</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>バックサイド ２階ホームエリア</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>サポーターズシート ２階ホームエリア</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>サポーターズシート １階ホームエリア</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>ファミリーシート２ １階ホームエリア</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ファミリーシート３ １階ホームエリア</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>ファミリーシート４ １階ホームエリア</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>ファミリーシートサイド２ １階ホームエリア</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>ファミリーシートサイド３ １階ホームエリア</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>ファミリーシートサイド４ １階ホームエリア</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>ホリデー席くじ１名セット</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>ホリデー席くじ２名セット</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>ホリデー席くじ４名セット</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>ビジターサポーターズシート ２階ビジターエリア</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>ビジターサポーターズシート １階ビジターエリア</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05 21:25</t>
+          <t>2026-10-17 06:02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>14,800</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6,400 完売</t>
+          <t>8,900 完売</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6,400 完売</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>8,000 完売</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,900 完売</t>
+          <t>8,100</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3,900 完売</t>
+          <t>8,100 完売</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>3,900</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
         <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-06 06:02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>6,400 完売</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>6,400 完売</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3,900 完売</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>3,900 完売</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-07 06:01</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>6,400 完売</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>6,400 完売</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3,900 完売</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3,900 完売</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-08 06:01</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>6,400 完売</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>6,400 完売</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3,900 完売</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>3,900 完売</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-09 16:40</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>3,200 完売</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>20,000 完売</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>20,000 完売</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-10 06:01</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>3,200 完売</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>20,000 完売</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>20,000 完売</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-11 06:01</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-12 06:01</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-13 06:01</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-14 06:01</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-15 06:01</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-16 06:01</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>7,900</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>6,400</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2,400</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>5,800</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>7,800</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>20,000</t>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>3,700</t>
         </is>
       </c>
     </row>
@@ -50500,7 +52882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50511,147 +52893,107 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>エキサイティングシート(ホーム)前方</t>
+          <t>ロイヤルシート</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>エキサイティングシート（ホーム）</t>
+          <t>ＳＳ指定席 北側</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>ホームメイン北SS指定席前方</t>
+          <t>ＳＳ指定席 南側</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ホームメイン北SS指定席</t>
+          <t>Ｓ指定席</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ホームメイン南SS指定席前方</t>
+          <t>Ａ指定席 南側</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>ホームメイン南SS指定席</t>
+          <t>Ａ指定席 北側</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>ホームメイン北S指定席前方</t>
+          <t>Ｂ指定席</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>ホームメイン北S指定席</t>
+          <t>Ｃ指定席</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>ミックスメイン南S指定席前方</t>
+          <t>メイン３階指定席</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>ミックスメイン南S指定席</t>
+          <t>バック３階指定席</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>ホームメインセンターA指定席</t>
+          <t>メイン４階指定席</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>ホームメイン北A指定席</t>
+          <t>バック４階指定席</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>ホームメイン南A指定席</t>
+          <t>ゴール裏指定席１階北側</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>バックセンターシート下段ホーム</t>
+          <t>ゴール裏指定席２階北側</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>バックセンターシート上段ホーム</t>
+          <t>ゴール裏指定席１階南側</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>ホームバック北A指定席下段</t>
+          <t>アウェイ指定席</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>ホームバック北A指定席上段</t>
+          <t>セブン-イレブン最前列シート</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>ホームバック南A指定席下段</t>
+          <t>バラ席当日引換券</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>ホームバック南A指定席上段</t>
+          <t>ベビーカーファミリーシート Ｓスタンド</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>ホームバック北B指定席下段</t>
+          <t>テーブル付きシート</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>ホームバック北B指定席上段</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>ホームバック南B指定席下段</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>ホームバック南B指定席上段</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>ホームサポーター指定席</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>ホームサポーター自由席</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>ホーム南スタンド自由席</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>ビジターサポーター指定席</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>バリュープライスシートAホーム</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>バリュープライスシートBホーム</t>
+          <t>ベビーカーファミリーシート バックスタンド</t>
         </is>
       </c>
     </row>
@@ -50663,149 +53005,93 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13,100 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12,100</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9,400</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8,400</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8,500</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7,100</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>6,100</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5,600</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>4,700</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>5,200</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>3,500 完売</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>2,500</t>
-        </is>
-      </c>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -50815,149 +53101,93 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13,100 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12,100</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9,400</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8,400</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8,500</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7,500</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7,100</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>6,100</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5,600</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4,700</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>5,200</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>3,500 完売</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>2,500</t>
-        </is>
-      </c>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -50967,149 +53197,93 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13,500</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12,500</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9,800</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8,800</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8,600</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7,600</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7,400</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>6,400</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>5,000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>5,400</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>4,300</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>3,500 完売</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>2,500</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -51119,149 +53293,93 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13,500</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12,500</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9,800</t>
+          <t>6,400 完売</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8,800</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8,600</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7,600</t>
+          <t>3,900 完売</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7,400</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>6,400</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>5,800</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>5,000</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>5,400</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>4,300</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>3,500 完売</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>2,500</t>
-        </is>
-      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -51271,147 +53389,107 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13,600 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12,600</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>5,600 完売</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>3,200 完売</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>5,800</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>20,000 完売</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>7,800</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>2,500</t>
+          <t>20,000 完売</t>
         </is>
       </c>
     </row>
@@ -51423,147 +53501,107 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13,600 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12,600</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>7,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>6,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>5,600 完売</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>3,200 完売</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>5,800</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>20,000 完売</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>7,800</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>2,500</t>
+          <t>20,000 完売</t>
         </is>
       </c>
     </row>
@@ -51575,147 +53613,107 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13,600 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12,600</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>7,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>6,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>5,600 完売</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>5,800</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>7,800</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>2,500</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -51727,147 +53725,107 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14,200 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13,200</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9,200</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8,200</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6,600</t>
+          <t>3,400</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>4,900</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5,100</t>
+          <t>2,400</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>5,600 完売</t>
+          <t>2,800</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>4,300</t>
+          <t>2,600</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>4,000</t>
+          <t>3,200</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>3,700</t>
+          <t>5,800</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>4,100</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3,800</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>3,600</t>
+          <t>7,800</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3,200</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2,500</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -51879,147 +53837,107 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14,500 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13,500</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9,600</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8,600</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>7,800</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>6,800</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>5,300</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4,800</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>5,600 完売</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4,100</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4,000</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>3,700</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3,100</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2,600</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2,900</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>2,500</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -52031,147 +53949,107 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14,500 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13,500</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>9,700</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8,700</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>7,800</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>6,800</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>5,300</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>4,600</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>5,600 完売</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>2,900</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2,500</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2,900</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>2,500</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -52183,147 +54061,107 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14,500 完売</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13,500</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>6,400</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9,000</t>
+          <t>4,900</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9,700</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8,700</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6,000</t>
+          <t>3,900</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>7,800</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>6,800</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>4,900</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>5,300</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>4,600</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>5,600 完売</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>3,900</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>3,600</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>3,400</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3,000</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>2,900</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2,500</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2,900</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>2,800</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>1,500</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>3,800</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3,500</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>2,500</t>
+          <t>20,000</t>
         </is>
       </c>
     </row>
@@ -52335,9 +54173,2071 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AD14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート(ホーム)前方</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>エキサイティングシート（ホーム）</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席前方</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ホームメイン北SS指定席</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席前方</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ホームメイン南SS指定席</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席前方</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ホームメイン北S指定席</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席前方</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ミックスメイン南S指定席</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ホームメインセンターA指定席</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ホームメイン北A指定席</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ホームメイン南A指定席</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>バックセンターシート下段ホーム</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>バックセンターシート上段ホーム</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席下段</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホームバック北A指定席上段</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席下段</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ホームバック南A指定席上段</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席下段</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ホームバック北B指定席上段</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席下段</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ホームバック南B指定席上段</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ホームサポーター指定席</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ホームサポーター自由席</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ホーム南スタンド自由席</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ビジターサポーター指定席</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートAホーム</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>バリュープライスシートBホーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-05 21:25</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13,100 完売</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06 06:02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13,100 完売</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9,800</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-08 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>9,800</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3,500 完売</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:40</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13,600 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-10 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13,600 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-11 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13,600 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-12 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>14,200 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>9,200</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-13 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>14,500 完売</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-14 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9,700</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-15 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>9,700</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-16 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>13,500</t>
@@ -52474,6 +56374,158 @@
         </is>
       </c>
       <c r="AD13" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-17 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -20239,7 +20239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22297,6 +22297,149 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22308,7 +22451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:T15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23670,6 +23813,108 @@
         </is>
       </c>
       <c r="T14" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -23686,7 +23931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI17"/>
+  <dimension ref="A1:AI18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26665,6 +26910,183 @@
         </is>
       </c>
       <c r="AI17" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
@@ -26681,7 +27103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28470,6 +28892,113 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -28486,7 +29015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30390,6 +30919,118 @@
       <c r="V17" t="inlineStr">
         <is>
           <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>5,000</t>
         </is>
       </c>
     </row>
@@ -30404,7 +31045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31162,6 +31803,158 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15,300</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>15,000 完売</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -31178,7 +31971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31636,6 +32429,98 @@
         </is>
       </c>
       <c r="R5" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>10,900 [変動]</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>4,200 [変動]</t>
         </is>
@@ -31652,7 +32537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33154,6 +34039,118 @@
         </is>
       </c>
       <c r="V14" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -33170,7 +34167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33703,6 +34700,113 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>5,400</t>
         </is>
@@ -33719,7 +34823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36301,6 +37405,158 @@
         </is>
       </c>
       <c r="AD17" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:00</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2,800 完売</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -37397,7 +38653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI5"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38280,6 +39536,183 @@
         </is>
       </c>
       <c r="AI5" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -38296,7 +39729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38854,6 +40287,118 @@
         </is>
       </c>
       <c r="V5" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -38870,7 +40415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39953,6 +41498,223 @@
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
@@ -39969,7 +41731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41790,6 +43552,153 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -41801,7 +43710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42809,6 +44718,208 @@
         </is>
       </c>
       <c r="AN5" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
         <is>
           <t>4,100</t>
         </is>
@@ -42825,7 +44936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44327,6 +46438,118 @@
         </is>
       </c>
       <c r="V14" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -44343,7 +46566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF5"/>
+  <dimension ref="A1:AF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45151,6 +47374,168 @@
         </is>
       </c>
       <c r="AF5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
@@ -45167,7 +47552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45675,6 +48060,108 @@
         </is>
       </c>
       <c r="T5" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15,100</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -45691,7 +48178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46449,6 +48936,158 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>19,900 完売</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10,300 完売</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>10,200 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>11,800 完売</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>9,500</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>19,800</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -46465,7 +49104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47198,6 +49837,153 @@
         </is>
       </c>
       <c r="AC5" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,500 完売</t>
         </is>
@@ -49164,7 +51950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51746,6 +54532,158 @@
         </is>
       </c>
       <c r="AD17" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -51762,7 +54700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG4"/>
+  <dimension ref="A1:AG5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52428,6 +55366,173 @@
         </is>
       </c>
       <c r="AG4" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16,000 完売</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>33,000 完売</t>
         </is>
@@ -52444,7 +55549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP2"/>
+  <dimension ref="A1:AP3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52866,6 +55971,218 @@
         </is>
       </c>
       <c r="AP2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>14,800</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -52882,7 +56199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54384,6 +57701,118 @@
         </is>
       </c>
       <c r="V14" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -54400,7 +57829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD14"/>
+  <dimension ref="A1:AD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56526,6 +59955,158 @@
         </is>
       </c>
       <c r="AD14" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-18 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13,600 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8,400</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -22451,7 +22451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T15"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23915,6 +23915,108 @@
         </is>
       </c>
       <c r="T15" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -23931,7 +24033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI18"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27087,6 +27189,183 @@
         </is>
       </c>
       <c r="AI18" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
@@ -27103,7 +27382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28999,6 +29278,113 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -29015,7 +29401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31029,6 +31415,118 @@
         </is>
       </c>
       <c r="V18" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12,200</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -31045,7 +31543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31955,6 +32453,158 @@
         </is>
       </c>
       <c r="AD6" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15,300</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>15,000 完売</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -31971,7 +32621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32521,6 +33171,98 @@
         </is>
       </c>
       <c r="R6" t="inlineStr">
+        <is>
+          <t>4,200 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>10,900 [変動]</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>4,200 [変動]</t>
         </is>
@@ -32537,7 +33279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34151,6 +34893,118 @@
         </is>
       </c>
       <c r="V15" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -34167,7 +35021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34807,6 +35661,113 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>5,400</t>
         </is>
@@ -34823,7 +35784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD18"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37559,6 +38520,158 @@
       <c r="AD18" t="inlineStr">
         <is>
           <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
         </is>
       </c>
     </row>
@@ -38653,7 +39766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39713,6 +40826,183 @@
         </is>
       </c>
       <c r="AI6" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -39729,7 +41019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40399,6 +41689,118 @@
         </is>
       </c>
       <c r="V6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -40415,7 +41817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41715,6 +43117,223 @@
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>4,800</t>
         </is>
@@ -41731,7 +43350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43699,6 +45318,153 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43710,7 +45476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN6"/>
+  <dimension ref="A1:AN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44920,6 +46686,208 @@
         </is>
       </c>
       <c r="AN6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
         <is>
           <t>4,100</t>
         </is>
@@ -44936,7 +46904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46550,6 +48518,118 @@
         </is>
       </c>
       <c r="V15" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -46566,7 +48646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AF7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47536,6 +49616,168 @@
         </is>
       </c>
       <c r="AF6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
@@ -47552,7 +49794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48162,6 +50404,108 @@
         </is>
       </c>
       <c r="T6" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15,300</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>13,100</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -48178,7 +50522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49088,6 +51432,158 @@
         </is>
       </c>
       <c r="AD6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>19,900 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10,300 完売</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>7,600 完売</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>9,500</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>19,800</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -49104,7 +51600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49984,6 +52480,153 @@
         </is>
       </c>
       <c r="AC6" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3,600 完売</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,500 完売</t>
         </is>
@@ -51950,7 +54593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD18"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54684,6 +57327,158 @@
         </is>
       </c>
       <c r="AD18" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:00</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -54700,7 +57495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG5"/>
+  <dimension ref="A1:AG6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55533,6 +58328,173 @@
         </is>
       </c>
       <c r="AG5" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16,000 完売</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>33,000 完売</t>
         </is>
@@ -55549,7 +58511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP3"/>
+  <dimension ref="A1:AP4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56183,6 +59145,218 @@
         </is>
       </c>
       <c r="AP3" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>14,800</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -56199,7 +59373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57813,6 +60987,118 @@
         </is>
       </c>
       <c r="V15" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -57829,7 +61115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AD16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60107,6 +63393,158 @@
         </is>
       </c>
       <c r="AD15" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:01</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14,200 完売</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -22451,7 +22451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24017,6 +24017,108 @@
         </is>
       </c>
       <c r="T16" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -24033,7 +24135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AI20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27366,6 +27468,183 @@
         </is>
       </c>
       <c r="AI19" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
         <is>
           <t>6,000</t>
         </is>
@@ -27382,7 +27661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29385,6 +29664,113 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -29401,7 +29787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31527,6 +31913,118 @@
         </is>
       </c>
       <c r="V19" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12,200</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>7,600</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -31543,7 +32041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32605,6 +33103,158 @@
         </is>
       </c>
       <c r="AD7" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15,300</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>15,000 完売</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -32621,7 +33271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33265,6 +33915,98 @@
       <c r="R7" t="inlineStr">
         <is>
           <t>4,200 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>10,900 [変動]</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,300 [変動]</t>
         </is>
       </c>
     </row>
@@ -33279,7 +34021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35005,6 +35747,118 @@
         </is>
       </c>
       <c r="V16" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -35021,7 +35875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35768,6 +36622,113 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>5,400</t>
         </is>
@@ -35784,7 +36745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38670,6 +39631,158 @@
         </is>
       </c>
       <c r="AD19" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:00</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>3,000 完売</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -39766,7 +40879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41003,6 +42116,183 @@
         </is>
       </c>
       <c r="AI7" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -41019,7 +42309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41801,6 +43091,118 @@
         </is>
       </c>
       <c r="V7" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -41817,7 +43219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43336,6 +44738,223 @@
       <c r="AQ7" t="inlineStr">
         <is>
           <t>4,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>29,800 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>5,000</t>
         </is>
       </c>
     </row>
@@ -43350,7 +44969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45465,6 +47084,153 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45476,7 +47242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46888,6 +48654,208 @@
         </is>
       </c>
       <c r="AN7" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
         <is>
           <t>4,100</t>
         </is>
@@ -46904,7 +48872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48630,6 +50598,118 @@
         </is>
       </c>
       <c r="V16" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -48646,7 +50726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF7"/>
+  <dimension ref="A1:AF8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49778,6 +51858,168 @@
         </is>
       </c>
       <c r="AF7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
@@ -49794,7 +52036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50506,6 +52748,108 @@
         </is>
       </c>
       <c r="T7" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15,700</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>13,100</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -50522,7 +52866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51586,6 +53930,158 @@
       <c r="AD7" t="inlineStr">
         <is>
           <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>19,900 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10,300 完売</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>9,500</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>19,800</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
         </is>
       </c>
     </row>
@@ -51600,7 +54096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52627,6 +55123,153 @@
         </is>
       </c>
       <c r="AC7" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,500 完売</t>
         </is>
@@ -54593,7 +57236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57479,6 +60122,158 @@
         </is>
       </c>
       <c r="AD19" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -57495,7 +60290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG6"/>
+  <dimension ref="A1:AG7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58495,6 +61290,173 @@
         </is>
       </c>
       <c r="AG6" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16,000 完売</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>33,000 完売</t>
         </is>
@@ -58511,7 +61473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP4"/>
+  <dimension ref="A1:AP5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59357,6 +62319,218 @@
         </is>
       </c>
       <c r="AP4" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>14,800</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>10,100 完売</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>9,000 完売</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -59373,7 +62547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61099,6 +64273,118 @@
         </is>
       </c>
       <c r="V16" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -61115,7 +64401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:AD17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63545,6 +66831,158 @@
         </is>
       </c>
       <c r="AD16" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -22451,7 +22451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24119,6 +24119,108 @@
         </is>
       </c>
       <c r="T17" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -24135,7 +24237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI20"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27647,6 +27749,183 @@
       <c r="AI20" t="inlineStr">
         <is>
           <t>6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>8,300 完売</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>8,400 完売</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>4,900 完売</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
         </is>
       </c>
     </row>
@@ -27661,7 +27940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29771,6 +30050,113 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -29787,7 +30173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32027,6 +32413,118 @@
       <c r="V20" t="inlineStr">
         <is>
           <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12,200</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>9,100</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>7,700</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>5,100</t>
         </is>
       </c>
     </row>
@@ -32041,7 +32539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33255,6 +33753,158 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15,300</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>15,000 完売</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -33271,7 +33921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34007,6 +34657,98 @@
       <c r="R8" t="inlineStr">
         <is>
           <t>4,300 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>10,900 [変動]</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,400 [変動]</t>
         </is>
       </c>
     </row>
@@ -34021,7 +34763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35859,6 +36601,118 @@
         </is>
       </c>
       <c r="V17" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -35875,7 +36729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36729,6 +37583,113 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>5,400</t>
         </is>
@@ -36745,7 +37706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39783,6 +40744,158 @@
         </is>
       </c>
       <c r="AD20" t="inlineStr">
+        <is>
+          <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:00</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>3,000 完売</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>2,500 完売</t>
         </is>
@@ -40879,7 +41992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI8"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42293,6 +43406,183 @@
         </is>
       </c>
       <c r="AI8" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -42309,7 +43599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43203,6 +44493,118 @@
         </is>
       </c>
       <c r="V8" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -43219,7 +44621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44953,6 +46355,223 @@
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>29,800 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -44969,7 +46588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47231,6 +48850,153 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -47242,7 +49008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:AN9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48856,6 +50622,208 @@
         </is>
       </c>
       <c r="AN8" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
         <is>
           <t>4,100</t>
         </is>
@@ -48872,7 +50840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50710,6 +52678,118 @@
         </is>
       </c>
       <c r="V17" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -50726,7 +52806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF8"/>
+  <dimension ref="A1:AF9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52020,6 +54100,168 @@
         </is>
       </c>
       <c r="AF8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
@@ -52036,7 +54278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52850,6 +55092,108 @@
         </is>
       </c>
       <c r="T8" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15,400</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>13,100</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10,000 完売</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -52866,7 +55210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54080,6 +56424,158 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>19,900 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10,300 完売</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>13,200 完売</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>9,500</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>19,800</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>5,300 完売</t>
         </is>
@@ -54096,7 +56592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55270,6 +57766,153 @@
         </is>
       </c>
       <c r="AC8" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>5,400 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,500 完売</t>
         </is>
@@ -57236,7 +59879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60274,6 +62917,158 @@
         </is>
       </c>
       <c r="AD20" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -60290,7 +63085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG7"/>
+  <dimension ref="A1:AG8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61457,6 +64252,173 @@
         </is>
       </c>
       <c r="AG7" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16,000 完売</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>33,000 完売</t>
         </is>
@@ -61473,7 +64435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP5"/>
+  <dimension ref="A1:AP6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62531,6 +65493,218 @@
         </is>
       </c>
       <c r="AP5" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>14,800</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10,100 完売</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -62547,7 +65721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64385,6 +67559,118 @@
         </is>
       </c>
       <c r="V17" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -64401,7 +67687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66983,6 +70269,158 @@
         </is>
       </c>
       <c r="AD17" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -32539,7 +32539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33905,6 +33905,158 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15,300</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>15,000 完売</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -33921,7 +34073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34749,6 +34901,98 @@
       <c r="R9" t="inlineStr">
         <is>
           <t>4,400 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>10,900 [変動]</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,500 [変動]</t>
         </is>
       </c>
     </row>
@@ -34763,7 +35007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36713,6 +36957,118 @@
         </is>
       </c>
       <c r="V18" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -36729,7 +37085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37690,6 +38046,113 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>5,400</t>
         </is>
@@ -37706,7 +38169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40898,6 +41361,158 @@
       <c r="AD21" t="inlineStr">
         <is>
           <t>2,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>3,000 完売</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>2,500</t>
         </is>
       </c>
     </row>
@@ -41992,7 +42607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43583,6 +44198,183 @@
         </is>
       </c>
       <c r="AI9" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -43599,7 +44391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44605,6 +45397,118 @@
         </is>
       </c>
       <c r="V9" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -44621,7 +45525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46572,6 +47476,223 @@
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>29,800 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -46588,7 +47709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48997,6 +50118,153 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -49008,7 +50276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN9"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50824,6 +52092,208 @@
         </is>
       </c>
       <c r="AN9" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
         <is>
           <t>4,100</t>
         </is>
@@ -50840,7 +52310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52790,6 +54260,118 @@
         </is>
       </c>
       <c r="V18" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -52806,7 +54388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF9"/>
+  <dimension ref="A1:AF10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54262,6 +55844,168 @@
         </is>
       </c>
       <c r="AF9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
@@ -54278,7 +56022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55194,6 +56938,108 @@
         </is>
       </c>
       <c r="T9" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15,600</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10,600 完売</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -55210,7 +57056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56576,6 +58422,158 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>19,900 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10,300 完売</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>13,200 完売</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>19,800</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>5,300 完売</t>
         </is>
@@ -56592,7 +58590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57913,6 +59911,153 @@
         </is>
       </c>
       <c r="AC9" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,500 完売</t>
         </is>
@@ -59879,7 +62024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63069,6 +65214,158 @@
         </is>
       </c>
       <c r="AD21" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -63085,7 +65382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG8"/>
+  <dimension ref="A1:AG9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64419,6 +66716,173 @@
         </is>
       </c>
       <c r="AG8" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16,000 完売</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>33,000 完売</t>
         </is>
@@ -64435,7 +66899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP6"/>
+  <dimension ref="A1:AP7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65705,6 +68169,218 @@
         </is>
       </c>
       <c r="AP6" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>14,800</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10,100 完売</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8,800 完売</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>3,700</t>
         </is>
@@ -65721,7 +68397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67671,6 +70347,118 @@
         </is>
       </c>
       <c r="V18" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -67687,7 +70475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD18"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70421,6 +73209,158 @@
         </is>
       </c>
       <c r="AD18" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-22 06:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -32539,7 +32539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34057,6 +34057,158 @@
         </is>
       </c>
       <c r="AD10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15,300</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>15,000 完売</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>2,900</t>
         </is>
@@ -34073,7 +34225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34993,6 +35145,98 @@
       <c r="R10" t="inlineStr">
         <is>
           <t>4,500 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8,750</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>9,400 [変動]</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8,400 [変動]</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>14,300</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>10,900 [変動]</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>4,600 [変動]</t>
         </is>
       </c>
     </row>
@@ -35007,7 +35251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37069,6 +37313,118 @@
         </is>
       </c>
       <c r="V19" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -37085,7 +37441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38155,6 +38511,113 @@
       <c r="U10" t="inlineStr">
         <is>
           <t>5,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5,500</t>
         </is>
       </c>
     </row>
@@ -38169,7 +38632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41511,6 +41974,158 @@
         </is>
       </c>
       <c r="AD22" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>3,700 完売</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>3,000 完売</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -42607,7 +43222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AI11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44375,6 +44990,183 @@
         </is>
       </c>
       <c r="AI10" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -44391,7 +45183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45509,6 +46301,118 @@
         </is>
       </c>
       <c r="V10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -45525,7 +46429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47693,6 +48597,223 @@
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>29,800 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -47709,7 +48830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50265,6 +51386,153 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -50276,7 +51544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN10"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52294,6 +53562,208 @@
         </is>
       </c>
       <c r="AN10" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2,800 完売</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
         <is>
           <t>4,100</t>
         </is>
@@ -52310,7 +53780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54372,6 +55842,118 @@
         </is>
       </c>
       <c r="V19" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -54388,7 +55970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF10"/>
+  <dimension ref="A1:AF11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56006,6 +57588,168 @@
         </is>
       </c>
       <c r="AF10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
@@ -56022,7 +57766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57040,6 +58784,108 @@
         </is>
       </c>
       <c r="T10" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15,900</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>13,300</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>11,200 完売</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -57056,7 +58902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58574,6 +60420,158 @@
         </is>
       </c>
       <c r="AD10" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19,900 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10,300 完売</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>13,200 完売</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>13,200 完売</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>19,800</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
         <is>
           <t>5,300 完売</t>
         </is>
@@ -58590,7 +60588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60058,6 +62056,153 @@
         </is>
       </c>
       <c r="AC10" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,500 完売</t>
         </is>
@@ -62024,7 +64169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65366,6 +67511,158 @@
         </is>
       </c>
       <c r="AD22" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -65382,7 +67679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG9"/>
+  <dimension ref="A1:AG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66883,6 +69180,173 @@
         </is>
       </c>
       <c r="AG9" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16,000 完売</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>33,000 完売</t>
         </is>
@@ -66899,7 +69363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP7"/>
+  <dimension ref="A1:AP8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68383,6 +70847,218 @@
       <c r="AP7" t="inlineStr">
         <is>
           <t>3,700</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>14,800</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10,100 完売</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>3,800</t>
         </is>
       </c>
     </row>
@@ -68397,7 +71073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V19"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70459,6 +73135,118 @@
         </is>
       </c>
       <c r="V19" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -70475,7 +73263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73361,6 +76149,158 @@
         </is>
       </c>
       <c r="AD19" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-23 06:01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -32539,7 +32539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34211,6 +34211,158 @@
       <c r="AD11" t="inlineStr">
         <is>
           <t>2,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>13,200 完売</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>15,000 完売</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>3,400</t>
         </is>
       </c>
     </row>
@@ -34225,7 +34377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35237,6 +35389,98 @@
       <c r="R11" t="inlineStr">
         <is>
           <t>4,600 [変動]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>9,250</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,800 [変動]</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7,800 [変動]</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7,200 [変動]</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>6,600 [変動]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>14,300 完売</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>11,000 完売</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>10,900 [変動] 完売</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>4,400 [変動]</t>
         </is>
       </c>
     </row>
@@ -35251,7 +35495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37425,6 +37669,118 @@
         </is>
       </c>
       <c r="V20" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2,200</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -37441,7 +37797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38616,6 +38972,113 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>5,900 完売</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
@@ -38632,7 +39095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42126,6 +42589,158 @@
         </is>
       </c>
       <c r="AD23" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>12,000 完売</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>3,000 完売</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -43222,7 +43837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI11"/>
+  <dimension ref="A1:AI12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45167,6 +45782,183 @@
         </is>
       </c>
       <c r="AI11" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -45183,7 +45975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46413,6 +47205,118 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -46429,7 +47333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48814,6 +49718,223 @@
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>29,800 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -48830,7 +49951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51533,6 +52654,153 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -51544,7 +52812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53764,6 +55032,208 @@
         </is>
       </c>
       <c r="AN11" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
         <is>
           <t>4,100</t>
         </is>
@@ -53780,7 +55250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55954,6 +57424,118 @@
         </is>
       </c>
       <c r="V20" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -55970,7 +57552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF11"/>
+  <dimension ref="A1:AF12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57750,6 +59332,168 @@
         </is>
       </c>
       <c r="AF11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
@@ -57766,7 +59510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58886,6 +60630,108 @@
         </is>
       </c>
       <c r="T11" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15,900</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13,200</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>11,800 完売</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -58902,7 +60748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60572,6 +62418,158 @@
         </is>
       </c>
       <c r="AD11" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19,900 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10,300 完売</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>13,200 完売</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>13,200 完売</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>19,800</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
         <is>
           <t>5,300 完売</t>
         </is>
@@ -60588,7 +62586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62203,6 +64201,153 @@
         </is>
       </c>
       <c r="AC11" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,500 完売</t>
         </is>
@@ -64169,7 +66314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67663,6 +69808,158 @@
         </is>
       </c>
       <c r="AD23" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -67679,7 +69976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG10"/>
+  <dimension ref="A1:AG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69347,6 +71644,173 @@
         </is>
       </c>
       <c r="AG10" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16,000 完売</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
         <is>
           <t>33,000 完売</t>
         </is>
@@ -69363,7 +71827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP8"/>
+  <dimension ref="A1:AP9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71057,6 +73521,218 @@
         </is>
       </c>
       <c r="AP8" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>14,800</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>10,100 完売</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
@@ -71073,7 +73749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73247,6 +75923,118 @@
         </is>
       </c>
       <c r="V20" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -73263,7 +76051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76301,6 +79089,158 @@
         </is>
       </c>
       <c r="AD20" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-24 06:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -35495,7 +35495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37781,6 +37781,118 @@
         </is>
       </c>
       <c r="V21" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4,200 完売</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2,200 完売</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>3,000 完売</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2,400 完売</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2,200 完売</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2,800 完売</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>3,400 完売</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2,000 完売</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>20,000 完売</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>20,000 完売</t>
         </is>
@@ -37797,7 +37909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39079,6 +39191,113 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6,300</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>5,500</t>
         </is>
@@ -39095,7 +39314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD24"/>
+  <dimension ref="A1:AD25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42741,6 +42960,158 @@
         </is>
       </c>
       <c r="AD24" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13,000 完売</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>5,200 完売</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>4,600 完売</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>3,000 完売</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -43837,7 +44208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI12"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45959,6 +46330,183 @@
         </is>
       </c>
       <c r="AI12" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8,500 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7,300 完売</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>6,100 完売</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4,800 完売</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>6,000 完売</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>7,900 完売</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>7,700 完売</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
         <is>
           <t>8,000</t>
         </is>
@@ -45975,7 +46523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47317,6 +47865,118 @@
         </is>
       </c>
       <c r="V12" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -47333,7 +47993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49935,6 +50595,223 @@
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>29,800 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>12,500</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -49951,7 +50828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52801,6 +53678,153 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52812,7 +53836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN12"/>
+  <dimension ref="A1:AN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55234,6 +56258,208 @@
         </is>
       </c>
       <c r="AN12" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
         <is>
           <t>4,100</t>
         </is>
@@ -55250,7 +56476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57536,6 +58762,118 @@
         </is>
       </c>
       <c r="V21" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -57552,7 +58890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF12"/>
+  <dimension ref="A1:AF13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59494,6 +60832,168 @@
         </is>
       </c>
       <c r="AF12" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12,100</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>8,100</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>3,300</t>
         </is>
@@ -59510,7 +61010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60732,6 +62232,108 @@
         </is>
       </c>
       <c r="T12" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15,900</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13,300</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>6,900</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -60748,7 +62350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62570,6 +64172,158 @@
         </is>
       </c>
       <c r="AD12" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>19,900 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>10,300 完売</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>9,400</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>13,200 完売</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>13,200 完売</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>19,800</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>5,300 完売</t>
         </is>
@@ -62586,7 +64340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64348,6 +66102,153 @@
         </is>
       </c>
       <c r="AC12" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,500 完売</t>
         </is>
@@ -66314,7 +68215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD24"/>
+  <dimension ref="A1:AD25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69960,6 +71861,158 @@
         </is>
       </c>
       <c r="AD24" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -69976,7 +72029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AG12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71811,6 +73864,173 @@
         </is>
       </c>
       <c r="AG11" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16,000 完売</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
         <is>
           <t>33,000 完売</t>
         </is>
@@ -71827,7 +74047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP9"/>
+  <dimension ref="A1:AP10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73733,6 +75953,218 @@
         </is>
       </c>
       <c r="AP9" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:02</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>14,800</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>10,100 完売</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>10,100</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
@@ -73749,7 +76181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76035,6 +78467,118 @@
         </is>
       </c>
       <c r="V21" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -76051,7 +78595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79241,6 +81785,158 @@
         </is>
       </c>
       <c r="AD21" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-25 06:01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>9,600</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>8,600</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -51,6 +51,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="横浜FM-FC東京_1129" sheetId="42" state="visible" r:id="rId42"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名古屋-福岡_1129" sheetId="43" state="visible" r:id="rId43"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C大阪-水戸_1205" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="浦和-名古屋_1205" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="浦和-川崎F_1213" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="名古屋-水戸_1213" sheetId="47" state="visible" r:id="rId47"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46523,7 +46526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47977,6 +47980,118 @@
         </is>
       </c>
       <c r="V13" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -47993,7 +48108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50812,6 +50927,223 @@
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>29,800 完売</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -50828,7 +51160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53825,6 +54157,149 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -53836,7 +54311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN13"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56460,6 +56935,208 @@
         </is>
       </c>
       <c r="AN13" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
         <is>
           <t>4,100</t>
         </is>
@@ -56476,7 +57153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58874,6 +59551,118 @@
         </is>
       </c>
       <c r="V22" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -58890,7 +59679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF13"/>
+  <dimension ref="A1:AF14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60996,6 +61785,168 @@
       <c r="AF13" t="inlineStr">
         <is>
           <t>3,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10,100 完売</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10,100 完売</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>7,100 完売</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>7,100</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>3,900 完売</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3,800 完売</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4,400 完売</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>5,500 完売</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
         </is>
       </c>
     </row>
@@ -61010,7 +61961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62334,6 +63285,108 @@
         </is>
       </c>
       <c r="T13" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13,400</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13,200 完売</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>4,000 完売</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>4,000 完売</t>
         </is>
@@ -62350,7 +63403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AD14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64324,6 +65377,158 @@
         </is>
       </c>
       <c r="AD13" t="inlineStr">
+        <is>
+          <t>5,300 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>19,900 完売</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10,300 完売</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>7,400 完売</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>13,800 完売</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>5,700 完売</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>9,400 完売</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>5,100 完売</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>7,500 完売</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>13,200 完売</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>13,200 完売</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>9,500 完売</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>19,800 完売</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>6,200 完売</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
         <is>
           <t>5,300 完売</t>
         </is>
@@ -64340,7 +65545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66249,6 +67454,153 @@
         </is>
       </c>
       <c r="AC13" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>7,000 完売</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6,300 完売</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>7,200 完売</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>5,550 完売</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>5,350 完売</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>8,200 完売</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>3,080 完売</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>1,500 完売</t>
         </is>
@@ -68215,7 +69567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD25"/>
+  <dimension ref="A1:AD26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72013,6 +73365,158 @@
         </is>
       </c>
       <c r="AD25" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>11,100</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>8,300</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>7,300</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>5,800 完売</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
         <is>
           <t>2,500</t>
         </is>
@@ -72029,7 +73533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:AG13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74031,6 +75535,173 @@
         </is>
       </c>
       <c r="AG12" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15,800</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6,600</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5,000 完売</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>8,500</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13,700</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>7,500</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16,000 完売</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>33,000 完売</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
         <is>
           <t>33,000 完売</t>
         </is>
@@ -74047,7 +75718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP10"/>
+  <dimension ref="A1:AP11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76165,6 +77836,218 @@
         </is>
       </c>
       <c r="AP10" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>14,800</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10,100 完売</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10,100 完売</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>8,600 完売</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8,700 完売</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>4,600</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>3,800</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>3,800</t>
         </is>
@@ -76181,7 +78064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78579,6 +80462,118 @@
         </is>
       </c>
       <c r="V22" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -78595,7 +80590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81939,6 +83934,902 @@
       <c r="AD22" t="inlineStr">
         <is>
           <t>2,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>14,500 完売</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>13,500</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>9,700</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>8,700</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>5,400</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>5,600 完売</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ｓ指定席ロアー メインロアー南側</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Ｓ指定席ロアー メインロアー北側</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Ｓ指定席アッパー メインアッパー南側</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Ｓ指定席アッパー メインアッパー北側</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>レッズシート バックロアー中央</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ＳＡメイン北指定席 メインロアー北側</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ＳＡバック指定席 バックロアー中央</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ＳＡメイン南指定席 メインロアー南側</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>パノラマシート バックアッパー中央</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ＳＢ指定席 バックロアー北側</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ＳＢ指定席 バックロアー南側</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>メインアッパー指定席 メインアッパー南側</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>メインアッパー指定席 メインアッパー北側</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>バックアッパー指定席 バックアッパー南側</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>バックアッパー指定席 バックアッパー北側</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ウェルカムシート バックアッパー南側</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホーム自由席</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ファミリーシート バックロアー南側</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ファミリーシート（メイン） メインロアー南側</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ペアシート バックアッパー南側</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ｊｕｉｃｅ スペシャルシート メインアッパー北側</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ビジター指定席 メインアッパー南側</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>ビジター自由席</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2,650</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2,750</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2,751 完売</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ｓ指定席ロアー メインロアー北側</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Ｓ指定席ロアー メインロアー南側</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Ｓ指定席アッパー メインアッパー南側</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Ｓ指定席アッパー メインアッパー北側</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>レッズシート バックロアー中央</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ＳＡメイン北指定席 メインロアー北側</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ＳＡバック指定席 バックロアー中央</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ＳＡメイン南指定席 メインロアー南側</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>パノラマシート バックアッパー中央</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ＳＢ指定席 バックロアー北側</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ＳＢ指定席 バックロアー南側</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>メインアッパー指定席 メインアッパー北側</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>メインアッパー指定席 メインアッパー南側</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>バックアッパー指定席 バックアッパー北側</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>バックアッパー指定席 バックアッパー南側</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ウェルカムシート バックアッパー南側</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ホーム自由席</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ファミリーシート バックロアー南側</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ファミリーシート（メイン） メインロアー南側</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ペアシート バックアッパー南側</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ビジター自由席</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>ビジター指定席 メインアッパー南側</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6,500 完売</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6,200</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5,200</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>5,100</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3,700</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>checked_at</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ロイヤルシート</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ＳＳ指定席 北側</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ＳＳ指定席 南側</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Ｓ指定席</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Ａ指定席 南側</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ａ指定席 北側</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Ｂ指定席</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Ｃ指定席</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>メイン３階指定席</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>バック３階指定席</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>メイン４階指定席</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>バック４階指定席</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ゴール裏指定席１階北側</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ゴール裏指定席２階北側</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ゴール裏指定席１階南側</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>アウェイ指定席</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ベビーカーファミリーシート バックスタンド</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>バラ席当日引換券</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ベビーカーファミリーシート Ｓスタンド</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>セブン-イレブン最前列シート</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>テーブル付きシート</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-26 06:01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>7,800</t>
         </is>
       </c>
     </row>

--- a/ticket_prices.xlsx
+++ b/ticket_prices.xlsx
@@ -46526,7 +46526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48092,6 +48092,118 @@
         </is>
       </c>
       <c r="V14" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-27 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12,600</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7,200</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6,500</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4,700</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4,800</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5,300</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>5,300</t>
         </is>
@@ -48108,7 +48220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ14"/>
+  <dimension ref="A1:AQ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51144,6 +51256,223 @@
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-27 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>29,800 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>12,500 完売</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>7,800 完売</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>11,100 完売</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>6,700 完売</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6,700</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>4,000</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>3,100</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>2,900 完売</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>3,250 完売</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2,700 完売</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>2,950 完売</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
@@ -51160,7 +51489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC23"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54300,6 +54629,149 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-27 06:01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5,700</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>8,800</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>6,600 完売</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>4,200</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3,300</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1,540</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2,700</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>7,400</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>6,400 完売</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>6,900 完売</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>8,200</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>5,500</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1,500 完売</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -54311,7 +54783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN14"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57137,6 +57609,208 @@
         </is>
       </c>
       <c r="AN14" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-27 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>29,800</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>8,000 完売</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,100 完売</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>6,800</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>6,800 完売</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4,300</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>4,400</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>3,600</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>4,100</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2,600 完売</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>2,100</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>2,450</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>1,900</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>2,150</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2,900</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>11,600</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
         <is>
           <t>4,100</t>
         </is>
@@ -57153,7 +57827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59663,6 +60337,118 @@
         </is>
       </c>
       <c r="V23" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-27 06:01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>6,400</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>4,900</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3,900</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>3,400</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2,400</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2,600</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>3,200</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>5,800</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>20,000</t>
         </is>
@@ -59679,7 +60465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF14"/>
+  <dimension ref="A1:AF15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61945,6 +62731,168 @@
         </is>
       </c>
       <c r="AF14" t="inlineStr">
+        <is>
+          <t>3,300 完売</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-27 06:01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12,100 完売</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>10,100 完売</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10,100 完売</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8,900 完売</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8,900</t>
+        <